--- a/central.xlsx
+++ b/central.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\deepa\Box\BJP Bangalore South District Office\2025\SIR\Notice hearing\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2f3df39ef44ce0b8/Desktop/Jayanagar/notice dashboard/deepseek/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23490ED6-D9AD-4106-A6CC-E35CC4EECACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{23490ED6-D9AD-4106-A6CC-E35CC4EECACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8315E9C-B7C9-4E7C-8781-1377932C3ECE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -475,6 +475,7 @@
   <dimension ref="A1:N1674"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
+    <col min="3" max="3" width="14.59765625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.3984375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.59765625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.3984375" customWidth="1"/>
@@ -19764,7 +19765,7 @@
         <v>20</v>
       </c>
       <c r="D439" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E439" t="s">
         <v>12</v>
@@ -19808,7 +19809,7 @@
         <v>20</v>
       </c>
       <c r="D440" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E440" t="s">
         <v>12</v>
@@ -19852,7 +19853,7 @@
         <v>20</v>
       </c>
       <c r="D441" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E441" t="s">
         <v>12</v>
@@ -19896,7 +19897,7 @@
         <v>20</v>
       </c>
       <c r="D442" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E442" t="s">
         <v>12</v>
@@ -19940,7 +19941,7 @@
         <v>20</v>
       </c>
       <c r="D443" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E443" t="s">
         <v>12</v>
@@ -19984,7 +19985,7 @@
         <v>20</v>
       </c>
       <c r="D444" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E444" t="s">
         <v>12</v>
@@ -20028,7 +20029,7 @@
         <v>20</v>
       </c>
       <c r="D445" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E445" t="s">
         <v>12</v>
@@ -20072,7 +20073,7 @@
         <v>20</v>
       </c>
       <c r="D446" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E446" t="s">
         <v>12</v>
@@ -20116,7 +20117,7 @@
         <v>20</v>
       </c>
       <c r="D447" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E447" t="s">
         <v>12</v>
@@ -20160,7 +20161,7 @@
         <v>20</v>
       </c>
       <c r="D448" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E448" t="s">
         <v>12</v>
@@ -20204,7 +20205,7 @@
         <v>20</v>
       </c>
       <c r="D449" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E449" t="s">
         <v>12</v>
@@ -20248,7 +20249,7 @@
         <v>20</v>
       </c>
       <c r="D450" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E450" t="s">
         <v>12</v>
@@ -20292,7 +20293,7 @@
         <v>20</v>
       </c>
       <c r="D451" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E451" t="s">
         <v>12</v>
@@ -20336,7 +20337,7 @@
         <v>20</v>
       </c>
       <c r="D452" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E452" t="s">
         <v>12</v>
@@ -20380,7 +20381,7 @@
         <v>20</v>
       </c>
       <c r="D453" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E453" t="s">
         <v>12</v>
@@ -20424,7 +20425,7 @@
         <v>20</v>
       </c>
       <c r="D454" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E454" t="s">
         <v>12</v>
@@ -20468,7 +20469,7 @@
         <v>20</v>
       </c>
       <c r="D455" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E455" t="s">
         <v>12</v>
@@ -20512,7 +20513,7 @@
         <v>20</v>
       </c>
       <c r="D456" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E456" t="s">
         <v>12</v>
@@ -20556,7 +20557,7 @@
         <v>20</v>
       </c>
       <c r="D457" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E457" t="s">
         <v>12</v>
@@ -20600,7 +20601,7 @@
         <v>20</v>
       </c>
       <c r="D458" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E458" t="s">
         <v>12</v>
@@ -20644,7 +20645,7 @@
         <v>20</v>
       </c>
       <c r="D459" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E459" t="s">
         <v>12</v>
@@ -20688,7 +20689,7 @@
         <v>20</v>
       </c>
       <c r="D460" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E460" t="s">
         <v>12</v>
@@ -20732,7 +20733,7 @@
         <v>20</v>
       </c>
       <c r="D461" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E461" t="s">
         <v>12</v>
@@ -20776,7 +20777,7 @@
         <v>20</v>
       </c>
       <c r="D462" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E462" t="s">
         <v>12</v>
@@ -20820,7 +20821,7 @@
         <v>20</v>
       </c>
       <c r="D463" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E463" t="s">
         <v>12</v>
@@ -20864,7 +20865,7 @@
         <v>20</v>
       </c>
       <c r="D464" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E464" t="s">
         <v>12</v>
@@ -20908,7 +20909,7 @@
         <v>20</v>
       </c>
       <c r="D465" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E465" t="s">
         <v>12</v>
@@ -20952,7 +20953,7 @@
         <v>20</v>
       </c>
       <c r="D466" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E466" t="s">
         <v>12</v>
@@ -20996,7 +20997,7 @@
         <v>20</v>
       </c>
       <c r="D467" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E467" t="s">
         <v>12</v>
@@ -21040,7 +21041,7 @@
         <v>20</v>
       </c>
       <c r="D468" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E468" t="s">
         <v>12</v>
@@ -21084,7 +21085,7 @@
         <v>20</v>
       </c>
       <c r="D469" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E469" t="s">
         <v>12</v>
@@ -21128,7 +21129,7 @@
         <v>20</v>
       </c>
       <c r="D470" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E470" t="s">
         <v>12</v>
@@ -21172,7 +21173,7 @@
         <v>20</v>
       </c>
       <c r="D471" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E471" t="s">
         <v>12</v>
@@ -21216,7 +21217,7 @@
         <v>20</v>
       </c>
       <c r="D472" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E472" t="s">
         <v>12</v>
@@ -21260,7 +21261,7 @@
         <v>20</v>
       </c>
       <c r="D473" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E473" t="s">
         <v>12</v>
@@ -21304,7 +21305,7 @@
         <v>20</v>
       </c>
       <c r="D474" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E474" t="s">
         <v>12</v>
@@ -21348,7 +21349,7 @@
         <v>20</v>
       </c>
       <c r="D475" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E475" t="s">
         <v>12</v>
@@ -21392,7 +21393,7 @@
         <v>20</v>
       </c>
       <c r="D476" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E476" t="s">
         <v>12</v>
@@ -21436,7 +21437,7 @@
         <v>20</v>
       </c>
       <c r="D477" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E477" t="s">
         <v>12</v>
@@ -21480,7 +21481,7 @@
         <v>20</v>
       </c>
       <c r="D478" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E478" t="s">
         <v>12</v>
@@ -21524,7 +21525,7 @@
         <v>20</v>
       </c>
       <c r="D479" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E479" t="s">
         <v>12</v>
@@ -21568,7 +21569,7 @@
         <v>20</v>
       </c>
       <c r="D480" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E480" t="s">
         <v>12</v>
@@ -21612,7 +21613,7 @@
         <v>20</v>
       </c>
       <c r="D481" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E481" t="s">
         <v>12</v>
@@ -21656,7 +21657,7 @@
         <v>20</v>
       </c>
       <c r="D482" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E482" t="s">
         <v>12</v>
@@ -21700,7 +21701,7 @@
         <v>20</v>
       </c>
       <c r="D483" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E483" t="s">
         <v>12</v>
@@ -21744,7 +21745,7 @@
         <v>20</v>
       </c>
       <c r="D484" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E484" t="s">
         <v>12</v>
@@ -21788,7 +21789,7 @@
         <v>20</v>
       </c>
       <c r="D485" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E485" t="s">
         <v>12</v>
@@ -21832,7 +21833,7 @@
         <v>20</v>
       </c>
       <c r="D486" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E486" t="s">
         <v>12</v>
@@ -21876,7 +21877,7 @@
         <v>20</v>
       </c>
       <c r="D487" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E487" t="s">
         <v>12</v>
@@ -21920,7 +21921,7 @@
         <v>20</v>
       </c>
       <c r="D488" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E488" t="s">
         <v>12</v>
@@ -21964,7 +21965,7 @@
         <v>20</v>
       </c>
       <c r="D489" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E489" t="s">
         <v>12</v>
@@ -22008,7 +22009,7 @@
         <v>20</v>
       </c>
       <c r="D490" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E490" t="s">
         <v>12</v>
@@ -22052,7 +22053,7 @@
         <v>20</v>
       </c>
       <c r="D491" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E491" t="s">
         <v>12</v>
@@ -22096,7 +22097,7 @@
         <v>20</v>
       </c>
       <c r="D492" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E492" t="s">
         <v>12</v>
@@ -22140,7 +22141,7 @@
         <v>20</v>
       </c>
       <c r="D493" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E493" t="s">
         <v>12</v>
@@ -22184,7 +22185,7 @@
         <v>20</v>
       </c>
       <c r="D494" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E494" t="s">
         <v>12</v>
@@ -22228,7 +22229,7 @@
         <v>20</v>
       </c>
       <c r="D495" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E495" t="s">
         <v>12</v>
@@ -22272,7 +22273,7 @@
         <v>20</v>
       </c>
       <c r="D496" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E496" t="s">
         <v>12</v>
@@ -22316,7 +22317,7 @@
         <v>20</v>
       </c>
       <c r="D497" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E497" t="s">
         <v>12</v>
@@ -22360,7 +22361,7 @@
         <v>20</v>
       </c>
       <c r="D498" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E498" t="s">
         <v>12</v>
@@ -22404,7 +22405,7 @@
         <v>20</v>
       </c>
       <c r="D499" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E499" t="s">
         <v>12</v>
@@ -22448,7 +22449,7 @@
         <v>20</v>
       </c>
       <c r="D500" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E500" t="s">
         <v>12</v>
@@ -22492,7 +22493,7 @@
         <v>20</v>
       </c>
       <c r="D501" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E501" t="s">
         <v>12</v>
@@ -22536,7 +22537,7 @@
         <v>20</v>
       </c>
       <c r="D502" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E502" t="s">
         <v>12</v>
@@ -22580,7 +22581,7 @@
         <v>20</v>
       </c>
       <c r="D503" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E503" t="s">
         <v>12</v>
@@ -22624,7 +22625,7 @@
         <v>20</v>
       </c>
       <c r="D504" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E504" t="s">
         <v>12</v>
@@ -22668,7 +22669,7 @@
         <v>20</v>
       </c>
       <c r="D505" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E505" t="s">
         <v>12</v>
@@ -22712,7 +22713,7 @@
         <v>20</v>
       </c>
       <c r="D506" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E506" t="s">
         <v>12</v>
@@ -22756,7 +22757,7 @@
         <v>20</v>
       </c>
       <c r="D507" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E507" t="s">
         <v>12</v>
@@ -22800,7 +22801,7 @@
         <v>20</v>
       </c>
       <c r="D508" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E508" t="s">
         <v>12</v>
@@ -22844,7 +22845,7 @@
         <v>20</v>
       </c>
       <c r="D509" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E509" t="s">
         <v>12</v>
@@ -22888,7 +22889,7 @@
         <v>20</v>
       </c>
       <c r="D510" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E510" t="s">
         <v>12</v>
@@ -22932,7 +22933,7 @@
         <v>20</v>
       </c>
       <c r="D511" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E511" t="s">
         <v>12</v>
@@ -22976,7 +22977,7 @@
         <v>20</v>
       </c>
       <c r="D512" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E512" t="s">
         <v>12</v>
@@ -23020,7 +23021,7 @@
         <v>20</v>
       </c>
       <c r="D513" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E513" t="s">
         <v>12</v>
@@ -23064,7 +23065,7 @@
         <v>20</v>
       </c>
       <c r="D514" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E514" t="s">
         <v>12</v>
@@ -23108,7 +23109,7 @@
         <v>20</v>
       </c>
       <c r="D515" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E515" t="s">
         <v>12</v>
@@ -23152,7 +23153,7 @@
         <v>20</v>
       </c>
       <c r="D516" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E516" t="s">
         <v>12</v>
@@ -23196,7 +23197,7 @@
         <v>20</v>
       </c>
       <c r="D517" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E517" t="s">
         <v>12</v>
@@ -23240,7 +23241,7 @@
         <v>20</v>
       </c>
       <c r="D518" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E518" t="s">
         <v>12</v>
@@ -23284,7 +23285,7 @@
         <v>20</v>
       </c>
       <c r="D519" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E519" t="s">
         <v>12</v>
@@ -23328,7 +23329,7 @@
         <v>20</v>
       </c>
       <c r="D520" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E520" t="s">
         <v>12</v>
@@ -23372,7 +23373,7 @@
         <v>20</v>
       </c>
       <c r="D521" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E521" t="s">
         <v>12</v>
@@ -23416,7 +23417,7 @@
         <v>20</v>
       </c>
       <c r="D522" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E522" t="s">
         <v>12</v>
@@ -23460,7 +23461,7 @@
         <v>20</v>
       </c>
       <c r="D523" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E523" t="s">
         <v>12</v>
@@ -23504,7 +23505,7 @@
         <v>20</v>
       </c>
       <c r="D524" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E524" t="s">
         <v>12</v>
@@ -23548,7 +23549,7 @@
         <v>20</v>
       </c>
       <c r="D525" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E525" t="s">
         <v>12</v>
@@ -23592,7 +23593,7 @@
         <v>20</v>
       </c>
       <c r="D526" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E526" t="s">
         <v>12</v>
@@ -23636,7 +23637,7 @@
         <v>20</v>
       </c>
       <c r="D527" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E527" t="s">
         <v>12</v>
@@ -23680,7 +23681,7 @@
         <v>20</v>
       </c>
       <c r="D528" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E528" t="s">
         <v>12</v>
@@ -23724,7 +23725,7 @@
         <v>20</v>
       </c>
       <c r="D529" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E529" t="s">
         <v>12</v>
@@ -23768,7 +23769,7 @@
         <v>20</v>
       </c>
       <c r="D530" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E530" t="s">
         <v>12</v>
@@ -23812,7 +23813,7 @@
         <v>20</v>
       </c>
       <c r="D531" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E531" t="s">
         <v>12</v>
@@ -23856,7 +23857,7 @@
         <v>20</v>
       </c>
       <c r="D532" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E532" t="s">
         <v>12</v>
@@ -23900,7 +23901,7 @@
         <v>20</v>
       </c>
       <c r="D533" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E533" t="s">
         <v>12</v>
@@ -23944,7 +23945,7 @@
         <v>20</v>
       </c>
       <c r="D534" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E534" t="s">
         <v>12</v>
@@ -23988,7 +23989,7 @@
         <v>20</v>
       </c>
       <c r="D535" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E535" t="s">
         <v>12</v>
@@ -24032,7 +24033,7 @@
         <v>20</v>
       </c>
       <c r="D536" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E536" t="s">
         <v>12</v>
@@ -24076,7 +24077,7 @@
         <v>20</v>
       </c>
       <c r="D537" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E537" t="s">
         <v>12</v>
@@ -24120,7 +24121,7 @@
         <v>20</v>
       </c>
       <c r="D538" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E538" t="s">
         <v>12</v>
@@ -24164,7 +24165,7 @@
         <v>20</v>
       </c>
       <c r="D539" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E539" t="s">
         <v>12</v>
@@ -24208,7 +24209,7 @@
         <v>20</v>
       </c>
       <c r="D540" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E540" t="s">
         <v>12</v>
@@ -24252,7 +24253,7 @@
         <v>20</v>
       </c>
       <c r="D541" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E541" t="s">
         <v>12</v>
@@ -24296,7 +24297,7 @@
         <v>20</v>
       </c>
       <c r="D542" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E542" t="s">
         <v>12</v>
@@ -24340,7 +24341,7 @@
         <v>20</v>
       </c>
       <c r="D543" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E543" t="s">
         <v>12</v>
@@ -24384,7 +24385,7 @@
         <v>20</v>
       </c>
       <c r="D544" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E544" t="s">
         <v>12</v>
@@ -24428,7 +24429,7 @@
         <v>20</v>
       </c>
       <c r="D545" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E545" t="s">
         <v>12</v>
@@ -24472,7 +24473,7 @@
         <v>20</v>
       </c>
       <c r="D546" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E546" t="s">
         <v>12</v>
@@ -24516,7 +24517,7 @@
         <v>20</v>
       </c>
       <c r="D547" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E547" t="s">
         <v>12</v>
@@ -24560,7 +24561,7 @@
         <v>20</v>
       </c>
       <c r="D548" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E548" t="s">
         <v>12</v>
@@ -24604,7 +24605,7 @@
         <v>20</v>
       </c>
       <c r="D549" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E549" t="s">
         <v>12</v>
@@ -24648,7 +24649,7 @@
         <v>20</v>
       </c>
       <c r="D550" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E550" t="s">
         <v>12</v>
@@ -24692,7 +24693,7 @@
         <v>20</v>
       </c>
       <c r="D551" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E551" t="s">
         <v>12</v>
@@ -24736,7 +24737,7 @@
         <v>20</v>
       </c>
       <c r="D552" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E552" t="s">
         <v>12</v>
@@ -24780,7 +24781,7 @@
         <v>20</v>
       </c>
       <c r="D553" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E553" t="s">
         <v>12</v>
@@ -24824,7 +24825,7 @@
         <v>20</v>
       </c>
       <c r="D554" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E554" t="s">
         <v>12</v>
@@ -24868,7 +24869,7 @@
         <v>20</v>
       </c>
       <c r="D555" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E555" t="s">
         <v>12</v>
@@ -24912,7 +24913,7 @@
         <v>20</v>
       </c>
       <c r="D556" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E556" t="s">
         <v>12</v>
@@ -24956,7 +24957,7 @@
         <v>20</v>
       </c>
       <c r="D557" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E557" t="s">
         <v>12</v>
@@ -25000,7 +25001,7 @@
         <v>20</v>
       </c>
       <c r="D558" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E558" t="s">
         <v>12</v>
@@ -25044,7 +25045,7 @@
         <v>20</v>
       </c>
       <c r="D559" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E559" t="s">
         <v>12</v>
@@ -25088,7 +25089,7 @@
         <v>20</v>
       </c>
       <c r="D560" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E560" t="s">
         <v>12</v>
@@ -25132,7 +25133,7 @@
         <v>20</v>
       </c>
       <c r="D561" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E561" t="s">
         <v>12</v>
@@ -25176,7 +25177,7 @@
         <v>20</v>
       </c>
       <c r="D562" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E562" t="s">
         <v>12</v>
@@ -25220,7 +25221,7 @@
         <v>20</v>
       </c>
       <c r="D563" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E563" t="s">
         <v>12</v>
@@ -25264,7 +25265,7 @@
         <v>20</v>
       </c>
       <c r="D564" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E564" t="s">
         <v>12</v>
@@ -25308,7 +25309,7 @@
         <v>20</v>
       </c>
       <c r="D565" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E565" t="s">
         <v>12</v>
@@ -25352,7 +25353,7 @@
         <v>20</v>
       </c>
       <c r="D566" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E566" t="s">
         <v>12</v>
@@ -25396,7 +25397,7 @@
         <v>20</v>
       </c>
       <c r="D567" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E567" t="s">
         <v>12</v>
@@ -25440,7 +25441,7 @@
         <v>20</v>
       </c>
       <c r="D568" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E568" t="s">
         <v>12</v>
@@ -25484,7 +25485,7 @@
         <v>20</v>
       </c>
       <c r="D569" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E569" t="s">
         <v>12</v>
@@ -25528,7 +25529,7 @@
         <v>20</v>
       </c>
       <c r="D570" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E570" t="s">
         <v>12</v>
@@ -25572,7 +25573,7 @@
         <v>20</v>
       </c>
       <c r="D571" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E571" t="s">
         <v>12</v>
@@ -25616,7 +25617,7 @@
         <v>20</v>
       </c>
       <c r="D572" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E572" t="s">
         <v>12</v>
@@ -25660,7 +25661,7 @@
         <v>20</v>
       </c>
       <c r="D573" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E573" t="s">
         <v>12</v>
@@ -25704,7 +25705,7 @@
         <v>20</v>
       </c>
       <c r="D574" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E574" t="s">
         <v>12</v>
@@ -25748,7 +25749,7 @@
         <v>20</v>
       </c>
       <c r="D575" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E575" t="s">
         <v>12</v>
@@ -25792,7 +25793,7 @@
         <v>20</v>
       </c>
       <c r="D576" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E576" t="s">
         <v>12</v>
@@ -25836,7 +25837,7 @@
         <v>20</v>
       </c>
       <c r="D577" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E577" t="s">
         <v>12</v>
@@ -25880,7 +25881,7 @@
         <v>20</v>
       </c>
       <c r="D578" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E578" t="s">
         <v>12</v>
@@ -25924,7 +25925,7 @@
         <v>20</v>
       </c>
       <c r="D579" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E579" t="s">
         <v>12</v>
@@ -25968,7 +25969,7 @@
         <v>20</v>
       </c>
       <c r="D580" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E580" t="s">
         <v>12</v>
@@ -26012,7 +26013,7 @@
         <v>20</v>
       </c>
       <c r="D581" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E581" t="s">
         <v>12</v>
@@ -26056,7 +26057,7 @@
         <v>20</v>
       </c>
       <c r="D582" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E582" t="s">
         <v>12</v>
@@ -26100,7 +26101,7 @@
         <v>20</v>
       </c>
       <c r="D583" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E583" t="s">
         <v>12</v>
@@ -26144,7 +26145,7 @@
         <v>20</v>
       </c>
       <c r="D584" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E584" t="s">
         <v>12</v>
@@ -26188,7 +26189,7 @@
         <v>20</v>
       </c>
       <c r="D585" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E585" t="s">
         <v>12</v>
@@ -26232,7 +26233,7 @@
         <v>20</v>
       </c>
       <c r="D586" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E586" t="s">
         <v>12</v>
@@ -26276,7 +26277,7 @@
         <v>20</v>
       </c>
       <c r="D587" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E587" t="s">
         <v>12</v>
@@ -26320,7 +26321,7 @@
         <v>20</v>
       </c>
       <c r="D588" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E588" t="s">
         <v>12</v>
@@ -26364,7 +26365,7 @@
         <v>20</v>
       </c>
       <c r="D589" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E589" t="s">
         <v>12</v>
@@ -26408,7 +26409,7 @@
         <v>20</v>
       </c>
       <c r="D590" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E590" t="s">
         <v>12</v>
@@ -26452,7 +26453,7 @@
         <v>20</v>
       </c>
       <c r="D591" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E591" t="s">
         <v>12</v>
@@ -26496,7 +26497,7 @@
         <v>20</v>
       </c>
       <c r="D592" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E592" t="s">
         <v>12</v>
@@ -26540,7 +26541,7 @@
         <v>20</v>
       </c>
       <c r="D593" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E593" t="s">
         <v>12</v>
@@ -26584,7 +26585,7 @@
         <v>20</v>
       </c>
       <c r="D594" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E594" t="s">
         <v>12</v>
@@ -26628,7 +26629,7 @@
         <v>20</v>
       </c>
       <c r="D595" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E595" t="s">
         <v>12</v>
@@ -26672,7 +26673,7 @@
         <v>20</v>
       </c>
       <c r="D596" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E596" t="s">
         <v>12</v>
@@ -26716,7 +26717,7 @@
         <v>20</v>
       </c>
       <c r="D597" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E597" t="s">
         <v>12</v>
@@ -26760,7 +26761,7 @@
         <v>20</v>
       </c>
       <c r="D598" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E598" t="s">
         <v>12</v>
@@ -26804,7 +26805,7 @@
         <v>20</v>
       </c>
       <c r="D599" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E599" t="s">
         <v>12</v>
@@ -26848,7 +26849,7 @@
         <v>20</v>
       </c>
       <c r="D600" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E600" t="s">
         <v>12</v>
@@ -26892,7 +26893,7 @@
         <v>20</v>
       </c>
       <c r="D601" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E601" t="s">
         <v>12</v>
@@ -26936,7 +26937,7 @@
         <v>20</v>
       </c>
       <c r="D602" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E602" t="s">
         <v>12</v>
@@ -26980,7 +26981,7 @@
         <v>20</v>
       </c>
       <c r="D603" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E603" t="s">
         <v>12</v>
@@ -27024,7 +27025,7 @@
         <v>20</v>
       </c>
       <c r="D604" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E604" t="s">
         <v>12</v>
@@ -27068,7 +27069,7 @@
         <v>20</v>
       </c>
       <c r="D605" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E605" t="s">
         <v>12</v>
@@ -27112,7 +27113,7 @@
         <v>20</v>
       </c>
       <c r="D606" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E606" t="s">
         <v>12</v>
@@ -27156,7 +27157,7 @@
         <v>20</v>
       </c>
       <c r="D607" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E607" t="s">
         <v>12</v>
@@ -27200,7 +27201,7 @@
         <v>20</v>
       </c>
       <c r="D608" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E608" t="s">
         <v>12</v>
@@ -27244,7 +27245,7 @@
         <v>20</v>
       </c>
       <c r="D609" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E609" t="s">
         <v>12</v>
@@ -27288,7 +27289,7 @@
         <v>20</v>
       </c>
       <c r="D610" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E610" t="s">
         <v>12</v>
@@ -27332,7 +27333,7 @@
         <v>20</v>
       </c>
       <c r="D611" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E611" t="s">
         <v>12</v>
@@ -27376,7 +27377,7 @@
         <v>20</v>
       </c>
       <c r="D612" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E612" t="s">
         <v>12</v>
@@ -27420,7 +27421,7 @@
         <v>20</v>
       </c>
       <c r="D613" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E613" t="s">
         <v>12</v>
@@ -27464,7 +27465,7 @@
         <v>20</v>
       </c>
       <c r="D614" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E614" t="s">
         <v>12</v>
@@ -27508,7 +27509,7 @@
         <v>20</v>
       </c>
       <c r="D615" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E615" t="s">
         <v>12</v>
@@ -27552,7 +27553,7 @@
         <v>20</v>
       </c>
       <c r="D616" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E616" t="s">
         <v>12</v>
@@ -27596,7 +27597,7 @@
         <v>20</v>
       </c>
       <c r="D617" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E617" t="s">
         <v>12</v>
@@ -27640,7 +27641,7 @@
         <v>20</v>
       </c>
       <c r="D618" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E618" t="s">
         <v>12</v>
@@ -27684,7 +27685,7 @@
         <v>20</v>
       </c>
       <c r="D619" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E619" t="s">
         <v>12</v>
@@ -27728,7 +27729,7 @@
         <v>20</v>
       </c>
       <c r="D620" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E620" t="s">
         <v>12</v>
@@ -27772,7 +27773,7 @@
         <v>20</v>
       </c>
       <c r="D621" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E621" t="s">
         <v>12</v>
@@ -27816,7 +27817,7 @@
         <v>20</v>
       </c>
       <c r="D622" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E622" t="s">
         <v>12</v>
@@ -27860,7 +27861,7 @@
         <v>20</v>
       </c>
       <c r="D623" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E623" t="s">
         <v>12</v>
@@ -27904,7 +27905,7 @@
         <v>20</v>
       </c>
       <c r="D624" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E624" t="s">
         <v>12</v>
@@ -27948,7 +27949,7 @@
         <v>20</v>
       </c>
       <c r="D625" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E625" t="s">
         <v>12</v>
@@ -27992,7 +27993,7 @@
         <v>20</v>
       </c>
       <c r="D626" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E626" t="s">
         <v>12</v>
@@ -28036,7 +28037,7 @@
         <v>20</v>
       </c>
       <c r="D627" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E627" t="s">
         <v>12</v>
@@ -28080,7 +28081,7 @@
         <v>20</v>
       </c>
       <c r="D628" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E628" t="s">
         <v>12</v>
@@ -28124,7 +28125,7 @@
         <v>20</v>
       </c>
       <c r="D629" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E629" t="s">
         <v>12</v>
@@ -28168,7 +28169,7 @@
         <v>20</v>
       </c>
       <c r="D630" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E630" t="s">
         <v>13</v>
@@ -28212,7 +28213,7 @@
         <v>20</v>
       </c>
       <c r="D631" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E631" t="s">
         <v>13</v>
@@ -28256,7 +28257,7 @@
         <v>20</v>
       </c>
       <c r="D632" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E632" t="s">
         <v>13</v>
@@ -28300,7 +28301,7 @@
         <v>20</v>
       </c>
       <c r="D633" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E633" t="s">
         <v>13</v>
@@ -28344,7 +28345,7 @@
         <v>20</v>
       </c>
       <c r="D634" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E634" t="s">
         <v>13</v>
@@ -28388,7 +28389,7 @@
         <v>20</v>
       </c>
       <c r="D635" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E635" t="s">
         <v>13</v>
@@ -28432,7 +28433,7 @@
         <v>20</v>
       </c>
       <c r="D636" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E636" t="s">
         <v>13</v>
@@ -28476,7 +28477,7 @@
         <v>20</v>
       </c>
       <c r="D637" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E637" t="s">
         <v>13</v>
@@ -28520,7 +28521,7 @@
         <v>20</v>
       </c>
       <c r="D638" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E638" t="s">
         <v>13</v>
@@ -28564,7 +28565,7 @@
         <v>20</v>
       </c>
       <c r="D639" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E639" t="s">
         <v>13</v>
@@ -28608,7 +28609,7 @@
         <v>20</v>
       </c>
       <c r="D640" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E640" t="s">
         <v>13</v>
@@ -28652,7 +28653,7 @@
         <v>20</v>
       </c>
       <c r="D641" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E641" t="s">
         <v>13</v>
@@ -28696,7 +28697,7 @@
         <v>20</v>
       </c>
       <c r="D642" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E642" t="s">
         <v>13</v>
@@ -28740,7 +28741,7 @@
         <v>20</v>
       </c>
       <c r="D643" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E643" t="s">
         <v>13</v>
@@ -28784,7 +28785,7 @@
         <v>20</v>
       </c>
       <c r="D644" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E644" t="s">
         <v>13</v>
@@ -28828,7 +28829,7 @@
         <v>20</v>
       </c>
       <c r="D645" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E645" t="s">
         <v>13</v>
@@ -28872,7 +28873,7 @@
         <v>20</v>
       </c>
       <c r="D646" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E646" t="s">
         <v>13</v>
@@ -28916,7 +28917,7 @@
         <v>20</v>
       </c>
       <c r="D647" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E647" t="s">
         <v>13</v>
@@ -28960,7 +28961,7 @@
         <v>20</v>
       </c>
       <c r="D648" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E648" t="s">
         <v>13</v>
@@ -29004,7 +29005,7 @@
         <v>20</v>
       </c>
       <c r="D649" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E649" t="s">
         <v>13</v>
@@ -29048,7 +29049,7 @@
         <v>20</v>
       </c>
       <c r="D650" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E650" t="s">
         <v>13</v>
@@ -29092,7 +29093,7 @@
         <v>20</v>
       </c>
       <c r="D651" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E651" t="s">
         <v>13</v>
@@ -29136,7 +29137,7 @@
         <v>20</v>
       </c>
       <c r="D652" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E652" t="s">
         <v>13</v>
@@ -29180,7 +29181,7 @@
         <v>20</v>
       </c>
       <c r="D653" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E653" t="s">
         <v>13</v>
@@ -29224,7 +29225,7 @@
         <v>20</v>
       </c>
       <c r="D654" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E654" t="s">
         <v>13</v>
@@ -29268,7 +29269,7 @@
         <v>20</v>
       </c>
       <c r="D655" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E655" t="s">
         <v>13</v>
@@ -29312,7 +29313,7 @@
         <v>20</v>
       </c>
       <c r="D656" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E656" t="s">
         <v>13</v>
@@ -29356,7 +29357,7 @@
         <v>20</v>
       </c>
       <c r="D657" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E657" t="s">
         <v>13</v>
@@ -29400,7 +29401,7 @@
         <v>20</v>
       </c>
       <c r="D658" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E658" t="s">
         <v>13</v>
@@ -29444,7 +29445,7 @@
         <v>20</v>
       </c>
       <c r="D659" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E659" t="s">
         <v>13</v>
@@ -29488,7 +29489,7 @@
         <v>20</v>
       </c>
       <c r="D660" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E660" t="s">
         <v>13</v>
@@ -29532,7 +29533,7 @@
         <v>20</v>
       </c>
       <c r="D661" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E661" t="s">
         <v>13</v>
@@ -29576,7 +29577,7 @@
         <v>20</v>
       </c>
       <c r="D662" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E662" t="s">
         <v>13</v>
@@ -29620,7 +29621,7 @@
         <v>20</v>
       </c>
       <c r="D663" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E663" t="s">
         <v>13</v>
@@ -29664,7 +29665,7 @@
         <v>20</v>
       </c>
       <c r="D664" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E664" t="s">
         <v>13</v>
@@ -29708,7 +29709,7 @@
         <v>20</v>
       </c>
       <c r="D665" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E665" t="s">
         <v>13</v>
@@ -29752,7 +29753,7 @@
         <v>20</v>
       </c>
       <c r="D666" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E666" t="s">
         <v>13</v>
@@ -29796,7 +29797,7 @@
         <v>20</v>
       </c>
       <c r="D667" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E667" t="s">
         <v>13</v>
@@ -29840,7 +29841,7 @@
         <v>20</v>
       </c>
       <c r="D668" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E668" t="s">
         <v>13</v>
@@ -29884,7 +29885,7 @@
         <v>20</v>
       </c>
       <c r="D669" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E669" t="s">
         <v>13</v>
@@ -29928,7 +29929,7 @@
         <v>20</v>
       </c>
       <c r="D670" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E670" t="s">
         <v>13</v>
@@ -29972,7 +29973,7 @@
         <v>20</v>
       </c>
       <c r="D671" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E671" t="s">
         <v>13</v>
@@ -30016,7 +30017,7 @@
         <v>20</v>
       </c>
       <c r="D672" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E672" t="s">
         <v>13</v>
@@ -30060,7 +30061,7 @@
         <v>20</v>
       </c>
       <c r="D673" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E673" t="s">
         <v>13</v>
@@ -30104,7 +30105,7 @@
         <v>20</v>
       </c>
       <c r="D674" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E674" t="s">
         <v>13</v>
@@ -30148,7 +30149,7 @@
         <v>20</v>
       </c>
       <c r="D675" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E675" t="s">
         <v>13</v>
@@ -30192,7 +30193,7 @@
         <v>20</v>
       </c>
       <c r="D676" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E676" t="s">
         <v>13</v>
@@ -30236,7 +30237,7 @@
         <v>20</v>
       </c>
       <c r="D677" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E677" t="s">
         <v>13</v>
@@ -30280,7 +30281,7 @@
         <v>20</v>
       </c>
       <c r="D678" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E678" t="s">
         <v>13</v>
@@ -30324,7 +30325,7 @@
         <v>20</v>
       </c>
       <c r="D679" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E679" t="s">
         <v>13</v>
@@ -30368,7 +30369,7 @@
         <v>20</v>
       </c>
       <c r="D680" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E680" t="s">
         <v>13</v>
@@ -30412,7 +30413,7 @@
         <v>20</v>
       </c>
       <c r="D681" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E681" t="s">
         <v>13</v>
@@ -30456,7 +30457,7 @@
         <v>20</v>
       </c>
       <c r="D682" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E682" t="s">
         <v>13</v>
@@ -30500,7 +30501,7 @@
         <v>20</v>
       </c>
       <c r="D683" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E683" t="s">
         <v>13</v>
@@ -30544,7 +30545,7 @@
         <v>20</v>
       </c>
       <c r="D684" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E684" t="s">
         <v>13</v>
@@ -30588,7 +30589,7 @@
         <v>20</v>
       </c>
       <c r="D685" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E685" t="s">
         <v>13</v>
@@ -30632,7 +30633,7 @@
         <v>20</v>
       </c>
       <c r="D686" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E686" t="s">
         <v>13</v>
@@ -30676,7 +30677,7 @@
         <v>20</v>
       </c>
       <c r="D687" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E687" t="s">
         <v>13</v>
@@ -30720,7 +30721,7 @@
         <v>20</v>
       </c>
       <c r="D688" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E688" t="s">
         <v>13</v>
@@ -30764,7 +30765,7 @@
         <v>20</v>
       </c>
       <c r="D689" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E689" t="s">
         <v>13</v>
@@ -30808,7 +30809,7 @@
         <v>20</v>
       </c>
       <c r="D690" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E690" t="s">
         <v>13</v>
@@ -30852,7 +30853,7 @@
         <v>20</v>
       </c>
       <c r="D691" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E691" t="s">
         <v>13</v>
@@ -30896,7 +30897,7 @@
         <v>20</v>
       </c>
       <c r="D692" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E692" t="s">
         <v>13</v>
@@ -30940,7 +30941,7 @@
         <v>20</v>
       </c>
       <c r="D693" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E693" t="s">
         <v>13</v>
@@ -30984,7 +30985,7 @@
         <v>20</v>
       </c>
       <c r="D694" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E694" t="s">
         <v>13</v>
@@ -31028,7 +31029,7 @@
         <v>20</v>
       </c>
       <c r="D695" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E695" t="s">
         <v>13</v>
@@ -31072,7 +31073,7 @@
         <v>20</v>
       </c>
       <c r="D696" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E696" t="s">
         <v>13</v>
@@ -31116,7 +31117,7 @@
         <v>20</v>
       </c>
       <c r="D697" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E697" t="s">
         <v>13</v>
@@ -31160,7 +31161,7 @@
         <v>20</v>
       </c>
       <c r="D698" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E698" t="s">
         <v>13</v>
@@ -31204,7 +31205,7 @@
         <v>20</v>
       </c>
       <c r="D699" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E699" t="s">
         <v>13</v>
@@ -31248,7 +31249,7 @@
         <v>20</v>
       </c>
       <c r="D700" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E700" t="s">
         <v>13</v>
@@ -31292,7 +31293,7 @@
         <v>20</v>
       </c>
       <c r="D701" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E701" t="s">
         <v>13</v>
@@ -31336,7 +31337,7 @@
         <v>20</v>
       </c>
       <c r="D702" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E702" t="s">
         <v>13</v>
@@ -31380,7 +31381,7 @@
         <v>20</v>
       </c>
       <c r="D703" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E703" t="s">
         <v>13</v>
@@ -31424,7 +31425,7 @@
         <v>20</v>
       </c>
       <c r="D704" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E704" t="s">
         <v>13</v>
@@ -31468,7 +31469,7 @@
         <v>20</v>
       </c>
       <c r="D705" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E705" t="s">
         <v>13</v>
@@ -31512,7 +31513,7 @@
         <v>20</v>
       </c>
       <c r="D706" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E706" t="s">
         <v>13</v>
@@ -31556,7 +31557,7 @@
         <v>20</v>
       </c>
       <c r="D707" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E707" t="s">
         <v>13</v>
@@ -31600,7 +31601,7 @@
         <v>20</v>
       </c>
       <c r="D708" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E708" t="s">
         <v>13</v>
@@ -31644,7 +31645,7 @@
         <v>20</v>
       </c>
       <c r="D709" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E709" t="s">
         <v>13</v>
@@ -31688,7 +31689,7 @@
         <v>20</v>
       </c>
       <c r="D710" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E710" t="s">
         <v>13</v>
@@ -31732,7 +31733,7 @@
         <v>20</v>
       </c>
       <c r="D711" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E711" t="s">
         <v>13</v>
@@ -31776,7 +31777,7 @@
         <v>20</v>
       </c>
       <c r="D712" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E712" t="s">
         <v>13</v>
@@ -31820,7 +31821,7 @@
         <v>20</v>
       </c>
       <c r="D713" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E713" t="s">
         <v>13</v>
@@ -31864,7 +31865,7 @@
         <v>20</v>
       </c>
       <c r="D714" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E714" t="s">
         <v>13</v>
@@ -31908,7 +31909,7 @@
         <v>20</v>
       </c>
       <c r="D715" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E715" t="s">
         <v>13</v>
@@ -31952,7 +31953,7 @@
         <v>20</v>
       </c>
       <c r="D716" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E716" t="s">
         <v>13</v>
@@ -31996,7 +31997,7 @@
         <v>20</v>
       </c>
       <c r="D717" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E717" t="s">
         <v>13</v>
@@ -32040,7 +32041,7 @@
         <v>20</v>
       </c>
       <c r="D718" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E718" t="s">
         <v>13</v>
@@ -32084,7 +32085,7 @@
         <v>20</v>
       </c>
       <c r="D719" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E719" t="s">
         <v>13</v>
@@ -32128,7 +32129,7 @@
         <v>20</v>
       </c>
       <c r="D720" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E720" t="s">
         <v>13</v>
@@ -32172,7 +32173,7 @@
         <v>20</v>
       </c>
       <c r="D721" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E721" t="s">
         <v>13</v>
@@ -32216,7 +32217,7 @@
         <v>20</v>
       </c>
       <c r="D722" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E722" t="s">
         <v>13</v>
@@ -32260,7 +32261,7 @@
         <v>20</v>
       </c>
       <c r="D723" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E723" t="s">
         <v>13</v>
@@ -32304,7 +32305,7 @@
         <v>20</v>
       </c>
       <c r="D724" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E724" t="s">
         <v>13</v>
@@ -32348,7 +32349,7 @@
         <v>20</v>
       </c>
       <c r="D725" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E725" t="s">
         <v>13</v>
@@ -32392,7 +32393,7 @@
         <v>20</v>
       </c>
       <c r="D726" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E726" t="s">
         <v>13</v>
@@ -32436,7 +32437,7 @@
         <v>20</v>
       </c>
       <c r="D727" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E727" t="s">
         <v>13</v>
@@ -32480,7 +32481,7 @@
         <v>20</v>
       </c>
       <c r="D728" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E728" t="s">
         <v>13</v>
@@ -32524,7 +32525,7 @@
         <v>20</v>
       </c>
       <c r="D729" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E729" t="s">
         <v>13</v>
@@ -32568,7 +32569,7 @@
         <v>20</v>
       </c>
       <c r="D730" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E730" t="s">
         <v>13</v>
@@ -32612,7 +32613,7 @@
         <v>20</v>
       </c>
       <c r="D731" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E731" t="s">
         <v>13</v>
@@ -32656,7 +32657,7 @@
         <v>20</v>
       </c>
       <c r="D732" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E732" t="s">
         <v>13</v>
@@ -32700,7 +32701,7 @@
         <v>20</v>
       </c>
       <c r="D733" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E733" t="s">
         <v>13</v>
@@ -32744,7 +32745,7 @@
         <v>20</v>
       </c>
       <c r="D734" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E734" t="s">
         <v>13</v>
@@ -32788,7 +32789,7 @@
         <v>20</v>
       </c>
       <c r="D735" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E735" t="s">
         <v>13</v>
@@ -32832,7 +32833,7 @@
         <v>20</v>
       </c>
       <c r="D736" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E736" t="s">
         <v>13</v>
@@ -32876,7 +32877,7 @@
         <v>20</v>
       </c>
       <c r="D737" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E737" t="s">
         <v>13</v>
@@ -32920,7 +32921,7 @@
         <v>20</v>
       </c>
       <c r="D738" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E738" t="s">
         <v>13</v>
@@ -32964,7 +32965,7 @@
         <v>20</v>
       </c>
       <c r="D739" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E739" t="s">
         <v>13</v>
@@ -33008,7 +33009,7 @@
         <v>20</v>
       </c>
       <c r="D740" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E740" t="s">
         <v>13</v>
@@ -33052,7 +33053,7 @@
         <v>20</v>
       </c>
       <c r="D741" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E741" t="s">
         <v>13</v>
@@ -33096,7 +33097,7 @@
         <v>20</v>
       </c>
       <c r="D742" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E742" t="s">
         <v>13</v>
@@ -33140,7 +33141,7 @@
         <v>20</v>
       </c>
       <c r="D743" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E743" t="s">
         <v>13</v>
@@ -33184,7 +33185,7 @@
         <v>20</v>
       </c>
       <c r="D744" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E744" t="s">
         <v>13</v>
@@ -33228,7 +33229,7 @@
         <v>20</v>
       </c>
       <c r="D745" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E745" t="s">
         <v>13</v>
@@ -33272,7 +33273,7 @@
         <v>20</v>
       </c>
       <c r="D746" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E746" t="s">
         <v>13</v>
@@ -33316,7 +33317,7 @@
         <v>20</v>
       </c>
       <c r="D747" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E747" t="s">
         <v>13</v>
@@ -33360,7 +33361,7 @@
         <v>20</v>
       </c>
       <c r="D748" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E748" t="s">
         <v>13</v>
@@ -33404,7 +33405,7 @@
         <v>20</v>
       </c>
       <c r="D749" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E749" t="s">
         <v>13</v>
@@ -33448,7 +33449,7 @@
         <v>20</v>
       </c>
       <c r="D750" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E750" t="s">
         <v>13</v>
@@ -33492,7 +33493,7 @@
         <v>20</v>
       </c>
       <c r="D751" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E751" t="s">
         <v>13</v>
@@ -33536,7 +33537,7 @@
         <v>20</v>
       </c>
       <c r="D752" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E752" t="s">
         <v>13</v>
@@ -33580,7 +33581,7 @@
         <v>20</v>
       </c>
       <c r="D753" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E753" t="s">
         <v>13</v>
@@ -33624,7 +33625,7 @@
         <v>20</v>
       </c>
       <c r="D754" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E754" t="s">
         <v>13</v>
@@ -33668,7 +33669,7 @@
         <v>20</v>
       </c>
       <c r="D755" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E755" t="s">
         <v>13</v>
@@ -33712,7 +33713,7 @@
         <v>20</v>
       </c>
       <c r="D756" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E756" t="s">
         <v>13</v>
@@ -33756,7 +33757,7 @@
         <v>20</v>
       </c>
       <c r="D757" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E757" t="s">
         <v>13</v>
@@ -33800,7 +33801,7 @@
         <v>20</v>
       </c>
       <c r="D758" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E758" t="s">
         <v>13</v>
@@ -33844,7 +33845,7 @@
         <v>20</v>
       </c>
       <c r="D759" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E759" t="s">
         <v>13</v>
@@ -33888,7 +33889,7 @@
         <v>20</v>
       </c>
       <c r="D760" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E760" t="s">
         <v>13</v>
@@ -33932,7 +33933,7 @@
         <v>20</v>
       </c>
       <c r="D761" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E761" t="s">
         <v>13</v>
@@ -33976,7 +33977,7 @@
         <v>20</v>
       </c>
       <c r="D762" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E762" t="s">
         <v>13</v>
@@ -34020,7 +34021,7 @@
         <v>20</v>
       </c>
       <c r="D763" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E763" t="s">
         <v>13</v>
@@ -34064,7 +34065,7 @@
         <v>20</v>
       </c>
       <c r="D764" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E764" t="s">
         <v>13</v>
@@ -34108,7 +34109,7 @@
         <v>20</v>
       </c>
       <c r="D765" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E765" t="s">
         <v>13</v>
@@ -34152,7 +34153,7 @@
         <v>20</v>
       </c>
       <c r="D766" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E766" t="s">
         <v>13</v>
@@ -34196,7 +34197,7 @@
         <v>20</v>
       </c>
       <c r="D767" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E767" t="s">
         <v>13</v>
@@ -34240,7 +34241,7 @@
         <v>20</v>
       </c>
       <c r="D768" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E768" t="s">
         <v>13</v>
@@ -34284,7 +34285,7 @@
         <v>20</v>
       </c>
       <c r="D769" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E769" t="s">
         <v>13</v>
@@ -34328,7 +34329,7 @@
         <v>20</v>
       </c>
       <c r="D770" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E770" t="s">
         <v>13</v>
@@ -34372,7 +34373,7 @@
         <v>20</v>
       </c>
       <c r="D771" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E771" t="s">
         <v>13</v>
@@ -34416,7 +34417,7 @@
         <v>20</v>
       </c>
       <c r="D772" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E772" t="s">
         <v>13</v>
@@ -34460,7 +34461,7 @@
         <v>20</v>
       </c>
       <c r="D773" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E773" t="s">
         <v>13</v>
@@ -34504,7 +34505,7 @@
         <v>20</v>
       </c>
       <c r="D774" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E774" t="s">
         <v>13</v>
@@ -34548,7 +34549,7 @@
         <v>20</v>
       </c>
       <c r="D775" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E775" t="s">
         <v>13</v>
@@ -34592,7 +34593,7 @@
         <v>20</v>
       </c>
       <c r="D776" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E776" t="s">
         <v>13</v>
@@ -34636,7 +34637,7 @@
         <v>20</v>
       </c>
       <c r="D777" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E777" t="s">
         <v>13</v>
@@ -34680,7 +34681,7 @@
         <v>20</v>
       </c>
       <c r="D778" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E778" t="s">
         <v>13</v>
@@ -34724,7 +34725,7 @@
         <v>20</v>
       </c>
       <c r="D779" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E779" t="s">
         <v>13</v>
@@ -34768,7 +34769,7 @@
         <v>20</v>
       </c>
       <c r="D780" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E780" t="s">
         <v>13</v>
@@ -34812,7 +34813,7 @@
         <v>20</v>
       </c>
       <c r="D781" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E781" t="s">
         <v>13</v>
@@ -34856,7 +34857,7 @@
         <v>20</v>
       </c>
       <c r="D782" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E782" t="s">
         <v>13</v>
@@ -34900,7 +34901,7 @@
         <v>20</v>
       </c>
       <c r="D783" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E783" t="s">
         <v>13</v>
@@ -34944,7 +34945,7 @@
         <v>20</v>
       </c>
       <c r="D784" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E784" t="s">
         <v>13</v>
@@ -34988,7 +34989,7 @@
         <v>20</v>
       </c>
       <c r="D785" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E785" t="s">
         <v>13</v>
@@ -35032,7 +35033,7 @@
         <v>20</v>
       </c>
       <c r="D786" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E786" t="s">
         <v>13</v>
@@ -35076,7 +35077,7 @@
         <v>20</v>
       </c>
       <c r="D787" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E787" t="s">
         <v>13</v>
@@ -35120,7 +35121,7 @@
         <v>20</v>
       </c>
       <c r="D788" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E788" t="s">
         <v>13</v>
@@ -35164,7 +35165,7 @@
         <v>20</v>
       </c>
       <c r="D789" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E789" t="s">
         <v>13</v>
@@ -35208,7 +35209,7 @@
         <v>20</v>
       </c>
       <c r="D790" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E790" t="s">
         <v>13</v>
@@ -35252,7 +35253,7 @@
         <v>20</v>
       </c>
       <c r="D791" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E791" t="s">
         <v>13</v>
@@ -35296,7 +35297,7 @@
         <v>20</v>
       </c>
       <c r="D792" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E792" t="s">
         <v>13</v>
@@ -35340,7 +35341,7 @@
         <v>20</v>
       </c>
       <c r="D793" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E793" t="s">
         <v>13</v>
@@ -35384,7 +35385,7 @@
         <v>20</v>
       </c>
       <c r="D794" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E794" t="s">
         <v>13</v>
@@ -35428,7 +35429,7 @@
         <v>20</v>
       </c>
       <c r="D795" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E795" t="s">
         <v>13</v>
@@ -35472,7 +35473,7 @@
         <v>20</v>
       </c>
       <c r="D796" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E796" t="s">
         <v>13</v>
@@ -35516,7 +35517,7 @@
         <v>20</v>
       </c>
       <c r="D797" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E797" t="s">
         <v>13</v>
@@ -35560,7 +35561,7 @@
         <v>20</v>
       </c>
       <c r="D798" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E798" t="s">
         <v>13</v>
@@ -35604,7 +35605,7 @@
         <v>20</v>
       </c>
       <c r="D799" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E799" t="s">
         <v>13</v>
@@ -35648,7 +35649,7 @@
         <v>20</v>
       </c>
       <c r="D800" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E800" t="s">
         <v>13</v>
@@ -35692,7 +35693,7 @@
         <v>20</v>
       </c>
       <c r="D801" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E801" t="s">
         <v>13</v>
@@ -35736,7 +35737,7 @@
         <v>20</v>
       </c>
       <c r="D802" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E802" t="s">
         <v>13</v>
@@ -35780,7 +35781,7 @@
         <v>20</v>
       </c>
       <c r="D803" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E803" t="s">
         <v>13</v>
@@ -35824,7 +35825,7 @@
         <v>20</v>
       </c>
       <c r="D804" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E804" t="s">
         <v>13</v>
@@ -35868,7 +35869,7 @@
         <v>20</v>
       </c>
       <c r="D805" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E805" t="s">
         <v>13</v>
@@ -35912,7 +35913,7 @@
         <v>20</v>
       </c>
       <c r="D806" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E806" t="s">
         <v>13</v>
@@ -35956,7 +35957,7 @@
         <v>20</v>
       </c>
       <c r="D807" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E807" t="s">
         <v>13</v>
@@ -36000,7 +36001,7 @@
         <v>20</v>
       </c>
       <c r="D808" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E808" t="s">
         <v>13</v>
@@ -36044,7 +36045,7 @@
         <v>20</v>
       </c>
       <c r="D809" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E809" t="s">
         <v>13</v>
@@ -36088,7 +36089,7 @@
         <v>20</v>
       </c>
       <c r="D810" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E810" t="s">
         <v>13</v>
@@ -36132,7 +36133,7 @@
         <v>20</v>
       </c>
       <c r="D811" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E811" t="s">
         <v>13</v>
@@ -36176,7 +36177,7 @@
         <v>20</v>
       </c>
       <c r="D812" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E812" t="s">
         <v>13</v>
@@ -36220,7 +36221,7 @@
         <v>20</v>
       </c>
       <c r="D813" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E813" t="s">
         <v>13</v>
@@ -36264,7 +36265,7 @@
         <v>20</v>
       </c>
       <c r="D814" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E814" t="s">
         <v>13</v>
@@ -36308,7 +36309,7 @@
         <v>20</v>
       </c>
       <c r="D815" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E815" t="s">
         <v>13</v>
@@ -36352,7 +36353,7 @@
         <v>20</v>
       </c>
       <c r="D816" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E816" t="s">
         <v>13</v>
@@ -36396,7 +36397,7 @@
         <v>20</v>
       </c>
       <c r="D817" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E817" t="s">
         <v>13</v>
@@ -36440,7 +36441,7 @@
         <v>20</v>
       </c>
       <c r="D818" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E818" t="s">
         <v>13</v>
@@ -36484,7 +36485,7 @@
         <v>20</v>
       </c>
       <c r="D819" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E819" t="s">
         <v>13</v>
@@ -36528,7 +36529,7 @@
         <v>20</v>
       </c>
       <c r="D820" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E820" t="s">
         <v>13</v>
@@ -36572,7 +36573,7 @@
         <v>20</v>
       </c>
       <c r="D821" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E821" t="s">
         <v>13</v>
@@ -36616,7 +36617,7 @@
         <v>20</v>
       </c>
       <c r="D822" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E822" t="s">
         <v>13</v>
@@ -36660,7 +36661,7 @@
         <v>20</v>
       </c>
       <c r="D823" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E823" t="s">
         <v>14</v>
@@ -36704,7 +36705,7 @@
         <v>20</v>
       </c>
       <c r="D824" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E824" t="s">
         <v>14</v>
@@ -36748,7 +36749,7 @@
         <v>20</v>
       </c>
       <c r="D825" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E825" t="s">
         <v>14</v>
@@ -36792,7 +36793,7 @@
         <v>20</v>
       </c>
       <c r="D826" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E826" t="s">
         <v>14</v>
@@ -36836,7 +36837,7 @@
         <v>20</v>
       </c>
       <c r="D827" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E827" t="s">
         <v>14</v>
@@ -36880,7 +36881,7 @@
         <v>20</v>
       </c>
       <c r="D828" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E828" t="s">
         <v>14</v>
@@ -36924,7 +36925,7 @@
         <v>20</v>
       </c>
       <c r="D829" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E829" t="s">
         <v>14</v>
@@ -36968,7 +36969,7 @@
         <v>20</v>
       </c>
       <c r="D830" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E830" t="s">
         <v>14</v>
@@ -37012,7 +37013,7 @@
         <v>20</v>
       </c>
       <c r="D831" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E831" t="s">
         <v>14</v>
@@ -37056,7 +37057,7 @@
         <v>20</v>
       </c>
       <c r="D832" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E832" t="s">
         <v>14</v>
@@ -37100,7 +37101,7 @@
         <v>20</v>
       </c>
       <c r="D833" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E833" t="s">
         <v>14</v>
@@ -37144,7 +37145,7 @@
         <v>20</v>
       </c>
       <c r="D834" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E834" t="s">
         <v>14</v>
@@ -37188,7 +37189,7 @@
         <v>20</v>
       </c>
       <c r="D835" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E835" t="s">
         <v>14</v>
@@ -37232,7 +37233,7 @@
         <v>20</v>
       </c>
       <c r="D836" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E836" t="s">
         <v>14</v>
@@ -37276,7 +37277,7 @@
         <v>20</v>
       </c>
       <c r="D837" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E837" t="s">
         <v>14</v>
@@ -37320,7 +37321,7 @@
         <v>20</v>
       </c>
       <c r="D838" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E838" t="s">
         <v>14</v>
@@ -37364,7 +37365,7 @@
         <v>20</v>
       </c>
       <c r="D839" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E839" t="s">
         <v>14</v>
@@ -37408,7 +37409,7 @@
         <v>20</v>
       </c>
       <c r="D840" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E840" t="s">
         <v>14</v>
@@ -37452,7 +37453,7 @@
         <v>20</v>
       </c>
       <c r="D841" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E841" t="s">
         <v>14</v>
@@ -37496,7 +37497,7 @@
         <v>20</v>
       </c>
       <c r="D842" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E842" t="s">
         <v>14</v>
@@ -37540,7 +37541,7 @@
         <v>20</v>
       </c>
       <c r="D843" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E843" t="s">
         <v>14</v>
@@ -37584,7 +37585,7 @@
         <v>20</v>
       </c>
       <c r="D844" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E844" t="s">
         <v>14</v>
@@ -37628,7 +37629,7 @@
         <v>20</v>
       </c>
       <c r="D845" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E845" t="s">
         <v>14</v>
@@ -37672,7 +37673,7 @@
         <v>20</v>
       </c>
       <c r="D846" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E846" t="s">
         <v>14</v>
@@ -37716,7 +37717,7 @@
         <v>20</v>
       </c>
       <c r="D847" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E847" t="s">
         <v>14</v>
@@ -37760,7 +37761,7 @@
         <v>20</v>
       </c>
       <c r="D848" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E848" t="s">
         <v>14</v>
@@ -37804,7 +37805,7 @@
         <v>20</v>
       </c>
       <c r="D849" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E849" t="s">
         <v>14</v>
@@ -37848,7 +37849,7 @@
         <v>20</v>
       </c>
       <c r="D850" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E850" t="s">
         <v>14</v>
@@ -37892,7 +37893,7 @@
         <v>20</v>
       </c>
       <c r="D851" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E851" t="s">
         <v>14</v>
@@ -37936,7 +37937,7 @@
         <v>20</v>
       </c>
       <c r="D852" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E852" t="s">
         <v>14</v>
@@ -37980,7 +37981,7 @@
         <v>20</v>
       </c>
       <c r="D853" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E853" t="s">
         <v>14</v>
@@ -38024,7 +38025,7 @@
         <v>20</v>
       </c>
       <c r="D854" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E854" t="s">
         <v>14</v>
@@ -38068,7 +38069,7 @@
         <v>20</v>
       </c>
       <c r="D855" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E855" t="s">
         <v>14</v>
@@ -38112,7 +38113,7 @@
         <v>20</v>
       </c>
       <c r="D856" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E856" t="s">
         <v>14</v>
@@ -38156,7 +38157,7 @@
         <v>20</v>
       </c>
       <c r="D857" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E857" t="s">
         <v>14</v>
@@ -38200,7 +38201,7 @@
         <v>20</v>
       </c>
       <c r="D858" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E858" t="s">
         <v>14</v>
@@ -38244,7 +38245,7 @@
         <v>20</v>
       </c>
       <c r="D859" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E859" t="s">
         <v>14</v>
@@ -38288,7 +38289,7 @@
         <v>20</v>
       </c>
       <c r="D860" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E860" t="s">
         <v>14</v>
@@ -38332,7 +38333,7 @@
         <v>20</v>
       </c>
       <c r="D861" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E861" t="s">
         <v>14</v>
@@ -38376,7 +38377,7 @@
         <v>20</v>
       </c>
       <c r="D862" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E862" t="s">
         <v>14</v>
@@ -38420,7 +38421,7 @@
         <v>20</v>
       </c>
       <c r="D863" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E863" t="s">
         <v>14</v>
@@ -38464,7 +38465,7 @@
         <v>20</v>
       </c>
       <c r="D864" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E864" t="s">
         <v>14</v>
@@ -38508,7 +38509,7 @@
         <v>20</v>
       </c>
       <c r="D865" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E865" t="s">
         <v>14</v>
@@ -38552,7 +38553,7 @@
         <v>20</v>
       </c>
       <c r="D866" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E866" t="s">
         <v>14</v>
@@ -38596,7 +38597,7 @@
         <v>20</v>
       </c>
       <c r="D867" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E867" t="s">
         <v>14</v>
@@ -38640,7 +38641,7 @@
         <v>20</v>
       </c>
       <c r="D868" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E868" t="s">
         <v>14</v>
@@ -38684,7 +38685,7 @@
         <v>20</v>
       </c>
       <c r="D869" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E869" t="s">
         <v>14</v>
@@ -38728,7 +38729,7 @@
         <v>20</v>
       </c>
       <c r="D870" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E870" t="s">
         <v>14</v>
@@ -38772,7 +38773,7 @@
         <v>20</v>
       </c>
       <c r="D871" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E871" t="s">
         <v>14</v>
@@ -38816,7 +38817,7 @@
         <v>20</v>
       </c>
       <c r="D872" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E872" t="s">
         <v>14</v>
@@ -38860,7 +38861,7 @@
         <v>20</v>
       </c>
       <c r="D873" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E873" t="s">
         <v>14</v>
@@ -38904,7 +38905,7 @@
         <v>20</v>
       </c>
       <c r="D874" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E874" t="s">
         <v>14</v>
@@ -38948,7 +38949,7 @@
         <v>20</v>
       </c>
       <c r="D875" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E875" t="s">
         <v>14</v>
@@ -38992,7 +38993,7 @@
         <v>20</v>
       </c>
       <c r="D876" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E876" t="s">
         <v>14</v>
@@ -39036,7 +39037,7 @@
         <v>20</v>
       </c>
       <c r="D877" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E877" t="s">
         <v>14</v>
@@ -39080,7 +39081,7 @@
         <v>20</v>
       </c>
       <c r="D878" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E878" t="s">
         <v>14</v>
@@ -39124,7 +39125,7 @@
         <v>20</v>
       </c>
       <c r="D879" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E879" t="s">
         <v>14</v>
@@ -39168,7 +39169,7 @@
         <v>20</v>
       </c>
       <c r="D880" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E880" t="s">
         <v>14</v>
@@ -39212,7 +39213,7 @@
         <v>20</v>
       </c>
       <c r="D881" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E881" t="s">
         <v>14</v>
@@ -39256,7 +39257,7 @@
         <v>20</v>
       </c>
       <c r="D882" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E882" t="s">
         <v>14</v>
@@ -39300,7 +39301,7 @@
         <v>20</v>
       </c>
       <c r="D883" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E883" t="s">
         <v>14</v>
@@ -39344,7 +39345,7 @@
         <v>20</v>
       </c>
       <c r="D884" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E884" t="s">
         <v>14</v>
@@ -39388,7 +39389,7 @@
         <v>20</v>
       </c>
       <c r="D885" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E885" t="s">
         <v>14</v>
@@ -39432,7 +39433,7 @@
         <v>20</v>
       </c>
       <c r="D886" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E886" t="s">
         <v>14</v>
@@ -39476,7 +39477,7 @@
         <v>20</v>
       </c>
       <c r="D887" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E887" t="s">
         <v>14</v>
@@ -39520,7 +39521,7 @@
         <v>20</v>
       </c>
       <c r="D888" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E888" t="s">
         <v>14</v>
@@ -39564,7 +39565,7 @@
         <v>20</v>
       </c>
       <c r="D889" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E889" t="s">
         <v>14</v>
@@ -39608,7 +39609,7 @@
         <v>20</v>
       </c>
       <c r="D890" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E890" t="s">
         <v>14</v>
@@ -39652,7 +39653,7 @@
         <v>20</v>
       </c>
       <c r="D891" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E891" t="s">
         <v>14</v>
@@ -39696,7 +39697,7 @@
         <v>20</v>
       </c>
       <c r="D892" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E892" t="s">
         <v>14</v>
@@ -39740,7 +39741,7 @@
         <v>20</v>
       </c>
       <c r="D893" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E893" t="s">
         <v>14</v>
@@ -39784,7 +39785,7 @@
         <v>20</v>
       </c>
       <c r="D894" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E894" t="s">
         <v>14</v>
@@ -39828,7 +39829,7 @@
         <v>20</v>
       </c>
       <c r="D895" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E895" t="s">
         <v>14</v>
@@ -39872,7 +39873,7 @@
         <v>20</v>
       </c>
       <c r="D896" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E896" t="s">
         <v>14</v>
@@ -39916,7 +39917,7 @@
         <v>20</v>
       </c>
       <c r="D897" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E897" t="s">
         <v>14</v>
@@ -39960,7 +39961,7 @@
         <v>20</v>
       </c>
       <c r="D898" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E898" t="s">
         <v>14</v>
@@ -40004,7 +40005,7 @@
         <v>20</v>
       </c>
       <c r="D899" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E899" t="s">
         <v>14</v>
@@ -40048,7 +40049,7 @@
         <v>20</v>
       </c>
       <c r="D900" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E900" t="s">
         <v>14</v>
@@ -40092,7 +40093,7 @@
         <v>20</v>
       </c>
       <c r="D901" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E901" t="s">
         <v>14</v>
@@ -40136,7 +40137,7 @@
         <v>20</v>
       </c>
       <c r="D902" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E902" t="s">
         <v>14</v>
@@ -40180,7 +40181,7 @@
         <v>20</v>
       </c>
       <c r="D903" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E903" t="s">
         <v>14</v>
@@ -40224,7 +40225,7 @@
         <v>20</v>
       </c>
       <c r="D904" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E904" t="s">
         <v>14</v>
@@ -40268,7 +40269,7 @@
         <v>20</v>
       </c>
       <c r="D905" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E905" t="s">
         <v>14</v>
@@ -40312,7 +40313,7 @@
         <v>20</v>
       </c>
       <c r="D906" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E906" t="s">
         <v>14</v>
@@ -40356,7 +40357,7 @@
         <v>20</v>
       </c>
       <c r="D907" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E907" t="s">
         <v>14</v>
@@ -40400,7 +40401,7 @@
         <v>20</v>
       </c>
       <c r="D908" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E908" t="s">
         <v>14</v>
@@ -40444,7 +40445,7 @@
         <v>20</v>
       </c>
       <c r="D909" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E909" t="s">
         <v>14</v>
@@ -40488,7 +40489,7 @@
         <v>20</v>
       </c>
       <c r="D910" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E910" t="s">
         <v>14</v>
@@ -40532,7 +40533,7 @@
         <v>20</v>
       </c>
       <c r="D911" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E911" t="s">
         <v>14</v>
@@ -40576,7 +40577,7 @@
         <v>20</v>
       </c>
       <c r="D912" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E912" t="s">
         <v>14</v>
@@ -40620,7 +40621,7 @@
         <v>20</v>
       </c>
       <c r="D913" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E913" t="s">
         <v>14</v>
@@ -40664,7 +40665,7 @@
         <v>20</v>
       </c>
       <c r="D914" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E914" t="s">
         <v>14</v>
@@ -40708,7 +40709,7 @@
         <v>20</v>
       </c>
       <c r="D915" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E915" t="s">
         <v>14</v>
@@ -40752,7 +40753,7 @@
         <v>20</v>
       </c>
       <c r="D916" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E916" t="s">
         <v>14</v>
@@ -40796,7 +40797,7 @@
         <v>20</v>
       </c>
       <c r="D917" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E917" t="s">
         <v>14</v>
@@ -40840,7 +40841,7 @@
         <v>20</v>
       </c>
       <c r="D918" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E918" t="s">
         <v>14</v>
@@ -40884,7 +40885,7 @@
         <v>20</v>
       </c>
       <c r="D919" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E919" t="s">
         <v>14</v>
@@ -40928,7 +40929,7 @@
         <v>20</v>
       </c>
       <c r="D920" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E920" t="s">
         <v>14</v>
@@ -40972,7 +40973,7 @@
         <v>20</v>
       </c>
       <c r="D921" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E921" t="s">
         <v>14</v>
@@ -41016,7 +41017,7 @@
         <v>20</v>
       </c>
       <c r="D922" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E922" t="s">
         <v>14</v>
@@ -41060,7 +41061,7 @@
         <v>20</v>
       </c>
       <c r="D923" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E923" t="s">
         <v>14</v>
@@ -41104,7 +41105,7 @@
         <v>20</v>
       </c>
       <c r="D924" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E924" t="s">
         <v>14</v>
@@ -41148,7 +41149,7 @@
         <v>20</v>
       </c>
       <c r="D925" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E925" t="s">
         <v>14</v>
@@ -41192,7 +41193,7 @@
         <v>20</v>
       </c>
       <c r="D926" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E926" t="s">
         <v>14</v>
@@ -41236,7 +41237,7 @@
         <v>20</v>
       </c>
       <c r="D927" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E927" t="s">
         <v>14</v>
@@ -41280,7 +41281,7 @@
         <v>20</v>
       </c>
       <c r="D928" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E928" t="s">
         <v>14</v>
@@ -41324,7 +41325,7 @@
         <v>20</v>
       </c>
       <c r="D929" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E929" t="s">
         <v>14</v>
@@ -41368,7 +41369,7 @@
         <v>20</v>
       </c>
       <c r="D930" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E930" t="s">
         <v>14</v>
@@ -41412,7 +41413,7 @@
         <v>20</v>
       </c>
       <c r="D931" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E931" t="s">
         <v>14</v>
@@ -41456,7 +41457,7 @@
         <v>20</v>
       </c>
       <c r="D932" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E932" t="s">
         <v>14</v>
@@ -41500,7 +41501,7 @@
         <v>20</v>
       </c>
       <c r="D933" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E933" t="s">
         <v>14</v>
@@ -41544,7 +41545,7 @@
         <v>20</v>
       </c>
       <c r="D934" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E934" t="s">
         <v>14</v>
@@ -41588,7 +41589,7 @@
         <v>20</v>
       </c>
       <c r="D935" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E935" t="s">
         <v>14</v>
@@ -41632,7 +41633,7 @@
         <v>20</v>
       </c>
       <c r="D936" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E936" t="s">
         <v>14</v>
@@ -41676,7 +41677,7 @@
         <v>20</v>
       </c>
       <c r="D937" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E937" t="s">
         <v>14</v>
@@ -41720,7 +41721,7 @@
         <v>20</v>
       </c>
       <c r="D938" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E938" t="s">
         <v>14</v>
@@ -41764,7 +41765,7 @@
         <v>20</v>
       </c>
       <c r="D939" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E939" t="s">
         <v>14</v>
@@ -41808,7 +41809,7 @@
         <v>20</v>
       </c>
       <c r="D940" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E940" t="s">
         <v>14</v>
@@ -41852,7 +41853,7 @@
         <v>20</v>
       </c>
       <c r="D941" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E941" t="s">
         <v>14</v>
@@ -41896,7 +41897,7 @@
         <v>20</v>
       </c>
       <c r="D942" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E942" t="s">
         <v>14</v>
@@ -41940,7 +41941,7 @@
         <v>20</v>
       </c>
       <c r="D943" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E943" t="s">
         <v>14</v>
@@ -41984,7 +41985,7 @@
         <v>20</v>
       </c>
       <c r="D944" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E944" t="s">
         <v>14</v>
@@ -42028,7 +42029,7 @@
         <v>20</v>
       </c>
       <c r="D945" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E945" t="s">
         <v>14</v>
@@ -42072,7 +42073,7 @@
         <v>20</v>
       </c>
       <c r="D946" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E946" t="s">
         <v>14</v>
@@ -42116,7 +42117,7 @@
         <v>20</v>
       </c>
       <c r="D947" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E947" t="s">
         <v>14</v>
@@ -42160,7 +42161,7 @@
         <v>20</v>
       </c>
       <c r="D948" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E948" t="s">
         <v>14</v>
@@ -42204,7 +42205,7 @@
         <v>20</v>
       </c>
       <c r="D949" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E949" t="s">
         <v>14</v>
@@ -42248,7 +42249,7 @@
         <v>20</v>
       </c>
       <c r="D950" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E950" t="s">
         <v>14</v>
@@ -42292,7 +42293,7 @@
         <v>20</v>
       </c>
       <c r="D951" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E951" t="s">
         <v>14</v>
@@ -42336,7 +42337,7 @@
         <v>20</v>
       </c>
       <c r="D952" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E952" t="s">
         <v>14</v>
@@ -42380,7 +42381,7 @@
         <v>20</v>
       </c>
       <c r="D953" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E953" t="s">
         <v>14</v>
@@ -42424,7 +42425,7 @@
         <v>20</v>
       </c>
       <c r="D954" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E954" t="s">
         <v>14</v>
@@ -42468,7 +42469,7 @@
         <v>20</v>
       </c>
       <c r="D955" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E955" t="s">
         <v>14</v>
@@ -42512,7 +42513,7 @@
         <v>20</v>
       </c>
       <c r="D956" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E956" t="s">
         <v>14</v>
@@ -42556,7 +42557,7 @@
         <v>20</v>
       </c>
       <c r="D957" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E957" t="s">
         <v>14</v>
@@ -42600,7 +42601,7 @@
         <v>20</v>
       </c>
       <c r="D958" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E958" t="s">
         <v>14</v>
@@ -42644,7 +42645,7 @@
         <v>20</v>
       </c>
       <c r="D959" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E959" t="s">
         <v>14</v>
@@ -42688,7 +42689,7 @@
         <v>20</v>
       </c>
       <c r="D960" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E960" t="s">
         <v>14</v>
@@ -42732,7 +42733,7 @@
         <v>20</v>
       </c>
       <c r="D961" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E961" t="s">
         <v>14</v>
@@ -42776,7 +42777,7 @@
         <v>20</v>
       </c>
       <c r="D962" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E962" t="s">
         <v>14</v>
@@ -42820,7 +42821,7 @@
         <v>20</v>
       </c>
       <c r="D963" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E963" t="s">
         <v>14</v>
@@ -42864,7 +42865,7 @@
         <v>20</v>
       </c>
       <c r="D964" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E964" t="s">
         <v>14</v>
@@ -42908,7 +42909,7 @@
         <v>20</v>
       </c>
       <c r="D965" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E965" t="s">
         <v>14</v>
@@ -42952,7 +42953,7 @@
         <v>20</v>
       </c>
       <c r="D966" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E966" t="s">
         <v>14</v>
@@ -42996,7 +42997,7 @@
         <v>20</v>
       </c>
       <c r="D967" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E967" t="s">
         <v>14</v>
@@ -43040,7 +43041,7 @@
         <v>20</v>
       </c>
       <c r="D968" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E968" t="s">
         <v>14</v>
@@ -43084,7 +43085,7 @@
         <v>20</v>
       </c>
       <c r="D969" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E969" t="s">
         <v>14</v>
@@ -43128,7 +43129,7 @@
         <v>20</v>
       </c>
       <c r="D970" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E970" t="s">
         <v>14</v>
@@ -43172,7 +43173,7 @@
         <v>20</v>
       </c>
       <c r="D971" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E971" t="s">
         <v>14</v>
@@ -43216,7 +43217,7 @@
         <v>20</v>
       </c>
       <c r="D972" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E972" t="s">
         <v>14</v>
@@ -43260,7 +43261,7 @@
         <v>20</v>
       </c>
       <c r="D973" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E973" t="s">
         <v>14</v>
@@ -43304,7 +43305,7 @@
         <v>20</v>
       </c>
       <c r="D974" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E974" t="s">
         <v>14</v>
@@ -43348,7 +43349,7 @@
         <v>20</v>
       </c>
       <c r="D975" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E975" t="s">
         <v>14</v>
@@ -43392,7 +43393,7 @@
         <v>20</v>
       </c>
       <c r="D976" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E976" t="s">
         <v>14</v>
@@ -43436,7 +43437,7 @@
         <v>20</v>
       </c>
       <c r="D977" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E977" t="s">
         <v>14</v>
@@ -43480,7 +43481,7 @@
         <v>20</v>
       </c>
       <c r="D978" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E978" t="s">
         <v>14</v>
@@ -43524,7 +43525,7 @@
         <v>20</v>
       </c>
       <c r="D979" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E979" t="s">
         <v>14</v>
@@ -43568,7 +43569,7 @@
         <v>20</v>
       </c>
       <c r="D980" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E980" t="s">
         <v>14</v>
@@ -43612,7 +43613,7 @@
         <v>20</v>
       </c>
       <c r="D981" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E981" t="s">
         <v>14</v>
@@ -43656,7 +43657,7 @@
         <v>20</v>
       </c>
       <c r="D982" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E982" t="s">
         <v>14</v>
@@ -43700,7 +43701,7 @@
         <v>20</v>
       </c>
       <c r="D983" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E983" t="s">
         <v>14</v>
@@ -43744,7 +43745,7 @@
         <v>20</v>
       </c>
       <c r="D984" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E984" t="s">
         <v>14</v>
@@ -43788,7 +43789,7 @@
         <v>20</v>
       </c>
       <c r="D985" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E985" t="s">
         <v>14</v>
@@ -43832,7 +43833,7 @@
         <v>20</v>
       </c>
       <c r="D986" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E986" t="s">
         <v>14</v>
@@ -43876,7 +43877,7 @@
         <v>20</v>
       </c>
       <c r="D987" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E987" t="s">
         <v>14</v>
@@ -43920,7 +43921,7 @@
         <v>20</v>
       </c>
       <c r="D988" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E988" t="s">
         <v>14</v>
@@ -43964,7 +43965,7 @@
         <v>20</v>
       </c>
       <c r="D989" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E989" t="s">
         <v>14</v>
@@ -44008,7 +44009,7 @@
         <v>20</v>
       </c>
       <c r="D990" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E990" t="s">
         <v>14</v>
@@ -44052,7 +44053,7 @@
         <v>20</v>
       </c>
       <c r="D991" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E991" t="s">
         <v>14</v>
@@ -44096,7 +44097,7 @@
         <v>20</v>
       </c>
       <c r="D992" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E992" t="s">
         <v>14</v>
@@ -44140,7 +44141,7 @@
         <v>20</v>
       </c>
       <c r="D993" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E993" t="s">
         <v>14</v>
@@ -44184,7 +44185,7 @@
         <v>20</v>
       </c>
       <c r="D994" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E994" t="s">
         <v>14</v>
@@ -44228,7 +44229,7 @@
         <v>20</v>
       </c>
       <c r="D995" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E995" t="s">
         <v>14</v>
@@ -44272,7 +44273,7 @@
         <v>20</v>
       </c>
       <c r="D996" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E996" t="s">
         <v>14</v>
@@ -44316,7 +44317,7 @@
         <v>20</v>
       </c>
       <c r="D997" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E997" t="s">
         <v>14</v>
@@ -44360,7 +44361,7 @@
         <v>20</v>
       </c>
       <c r="D998" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E998" t="s">
         <v>14</v>
@@ -44404,7 +44405,7 @@
         <v>20</v>
       </c>
       <c r="D999" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E999" t="s">
         <v>14</v>
@@ -44448,7 +44449,7 @@
         <v>20</v>
       </c>
       <c r="D1000" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1000" t="s">
         <v>14</v>
@@ -44492,7 +44493,7 @@
         <v>20</v>
       </c>
       <c r="D1001" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1001" t="s">
         <v>14</v>
@@ -44536,7 +44537,7 @@
         <v>20</v>
       </c>
       <c r="D1002" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1002" t="s">
         <v>14</v>
@@ -44580,7 +44581,7 @@
         <v>20</v>
       </c>
       <c r="D1003" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1003" t="s">
         <v>14</v>
@@ -44624,7 +44625,7 @@
         <v>20</v>
       </c>
       <c r="D1004" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1004" t="s">
         <v>14</v>
@@ -44668,7 +44669,7 @@
         <v>20</v>
       </c>
       <c r="D1005" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1005" t="s">
         <v>14</v>
@@ -44712,7 +44713,7 @@
         <v>20</v>
       </c>
       <c r="D1006" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1006" t="s">
         <v>14</v>
@@ -44756,7 +44757,7 @@
         <v>20</v>
       </c>
       <c r="D1007" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1007" t="s">
         <v>14</v>
@@ -44800,7 +44801,7 @@
         <v>20</v>
       </c>
       <c r="D1008" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1008" t="s">
         <v>14</v>
@@ -44844,7 +44845,7 @@
         <v>20</v>
       </c>
       <c r="D1009" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1009" t="s">
         <v>14</v>
@@ -44888,7 +44889,7 @@
         <v>20</v>
       </c>
       <c r="D1010" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1010" t="s">
         <v>14</v>
@@ -44932,7 +44933,7 @@
         <v>20</v>
       </c>
       <c r="D1011" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1011" t="s">
         <v>14</v>
@@ -44976,7 +44977,7 @@
         <v>20</v>
       </c>
       <c r="D1012" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1012" t="s">
         <v>14</v>
@@ -45020,7 +45021,7 @@
         <v>20</v>
       </c>
       <c r="D1013" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1013" t="s">
         <v>14</v>
@@ -45064,7 +45065,7 @@
         <v>20</v>
       </c>
       <c r="D1014" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1014" t="s">
         <v>14</v>
@@ -45108,7 +45109,7 @@
         <v>20</v>
       </c>
       <c r="D1015" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1015" t="s">
         <v>14</v>
@@ -45152,7 +45153,7 @@
         <v>20</v>
       </c>
       <c r="D1016" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1016" t="s">
         <v>14</v>
@@ -45196,7 +45197,7 @@
         <v>20</v>
       </c>
       <c r="D1017" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1017" t="s">
         <v>14</v>
@@ -45240,7 +45241,7 @@
         <v>20</v>
       </c>
       <c r="D1018" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1018" t="s">
         <v>14</v>
@@ -45284,7 +45285,7 @@
         <v>20</v>
       </c>
       <c r="D1019" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1019" t="s">
         <v>14</v>
@@ -45328,7 +45329,7 @@
         <v>20</v>
       </c>
       <c r="D1020" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1020" t="s">
         <v>14</v>
@@ -45372,7 +45373,7 @@
         <v>20</v>
       </c>
       <c r="D1021" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1021" t="s">
         <v>14</v>
@@ -45416,7 +45417,7 @@
         <v>20</v>
       </c>
       <c r="D1022" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1022" t="s">
         <v>14</v>
@@ -45460,7 +45461,7 @@
         <v>20</v>
       </c>
       <c r="D1023" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1023" t="s">
         <v>14</v>
@@ -45504,7 +45505,7 @@
         <v>20</v>
       </c>
       <c r="D1024" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1024" t="s">
         <v>14</v>
@@ -45548,7 +45549,7 @@
         <v>20</v>
       </c>
       <c r="D1025" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1025" t="s">
         <v>14</v>
@@ -45592,7 +45593,7 @@
         <v>20</v>
       </c>
       <c r="D1026" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1026" t="s">
         <v>14</v>
@@ -45636,7 +45637,7 @@
         <v>20</v>
       </c>
       <c r="D1027" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1027" t="s">
         <v>14</v>
@@ -45680,7 +45681,7 @@
         <v>20</v>
       </c>
       <c r="D1028" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1028" t="s">
         <v>14</v>
@@ -45724,7 +45725,7 @@
         <v>20</v>
       </c>
       <c r="D1029" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1029" t="s">
         <v>14</v>
@@ -45768,7 +45769,7 @@
         <v>20</v>
       </c>
       <c r="D1030" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1030" t="s">
         <v>14</v>
@@ -45812,7 +45813,7 @@
         <v>20</v>
       </c>
       <c r="D1031" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1031" t="s">
         <v>14</v>
@@ -45856,7 +45857,7 @@
         <v>20</v>
       </c>
       <c r="D1032" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1032" t="s">
         <v>14</v>
@@ -45900,7 +45901,7 @@
         <v>20</v>
       </c>
       <c r="D1033" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1033" t="s">
         <v>14</v>
@@ -45944,7 +45945,7 @@
         <v>20</v>
       </c>
       <c r="D1034" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1034" t="s">
         <v>14</v>
@@ -45988,7 +45989,7 @@
         <v>20</v>
       </c>
       <c r="D1035" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1035" t="s">
         <v>14</v>
@@ -46032,7 +46033,7 @@
         <v>20</v>
       </c>
       <c r="D1036" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1036" t="s">
         <v>14</v>
@@ -46076,7 +46077,7 @@
         <v>20</v>
       </c>
       <c r="D1037" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1037" t="s">
         <v>14</v>
@@ -46120,7 +46121,7 @@
         <v>20</v>
       </c>
       <c r="D1038" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1038" t="s">
         <v>14</v>
@@ -46164,7 +46165,7 @@
         <v>20</v>
       </c>
       <c r="D1039" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1039" t="s">
         <v>14</v>
@@ -46208,7 +46209,7 @@
         <v>20</v>
       </c>
       <c r="D1040" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1040" t="s">
         <v>14</v>
@@ -46252,7 +46253,7 @@
         <v>20</v>
       </c>
       <c r="D1041" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1041" t="s">
         <v>14</v>
@@ -46296,7 +46297,7 @@
         <v>20</v>
       </c>
       <c r="D1042" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1042" t="s">
         <v>14</v>
@@ -46340,7 +46341,7 @@
         <v>20</v>
       </c>
       <c r="D1043" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1043" t="s">
         <v>15</v>
@@ -46384,7 +46385,7 @@
         <v>20</v>
       </c>
       <c r="D1044" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1044" t="s">
         <v>15</v>
@@ -46428,7 +46429,7 @@
         <v>20</v>
       </c>
       <c r="D1045" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1045" t="s">
         <v>15</v>
@@ -46472,7 +46473,7 @@
         <v>20</v>
       </c>
       <c r="D1046" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1046" t="s">
         <v>15</v>
@@ -46516,7 +46517,7 @@
         <v>20</v>
       </c>
       <c r="D1047" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1047" t="s">
         <v>15</v>
@@ -46560,7 +46561,7 @@
         <v>20</v>
       </c>
       <c r="D1048" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1048" t="s">
         <v>15</v>
@@ -46604,7 +46605,7 @@
         <v>20</v>
       </c>
       <c r="D1049" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1049" t="s">
         <v>15</v>
@@ -46648,7 +46649,7 @@
         <v>20</v>
       </c>
       <c r="D1050" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1050" t="s">
         <v>15</v>
@@ -46692,7 +46693,7 @@
         <v>20</v>
       </c>
       <c r="D1051" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1051" t="s">
         <v>15</v>
@@ -46736,7 +46737,7 @@
         <v>20</v>
       </c>
       <c r="D1052" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1052" t="s">
         <v>15</v>
@@ -46780,7 +46781,7 @@
         <v>20</v>
       </c>
       <c r="D1053" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1053" t="s">
         <v>15</v>
@@ -46824,7 +46825,7 @@
         <v>20</v>
       </c>
       <c r="D1054" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1054" t="s">
         <v>15</v>
@@ -46868,7 +46869,7 @@
         <v>20</v>
       </c>
       <c r="D1055" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1055" t="s">
         <v>15</v>
@@ -46912,7 +46913,7 @@
         <v>20</v>
       </c>
       <c r="D1056" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1056" t="s">
         <v>15</v>
@@ -46956,7 +46957,7 @@
         <v>20</v>
       </c>
       <c r="D1057" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1057" t="s">
         <v>15</v>
@@ -47000,7 +47001,7 @@
         <v>20</v>
       </c>
       <c r="D1058" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1058" t="s">
         <v>15</v>
@@ -47044,7 +47045,7 @@
         <v>20</v>
       </c>
       <c r="D1059" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1059" t="s">
         <v>15</v>
@@ -47088,7 +47089,7 @@
         <v>20</v>
       </c>
       <c r="D1060" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1060" t="s">
         <v>15</v>
@@ -47132,7 +47133,7 @@
         <v>20</v>
       </c>
       <c r="D1061" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1061" t="s">
         <v>15</v>
@@ -47176,7 +47177,7 @@
         <v>20</v>
       </c>
       <c r="D1062" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1062" t="s">
         <v>15</v>
@@ -47220,7 +47221,7 @@
         <v>20</v>
       </c>
       <c r="D1063" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1063" t="s">
         <v>15</v>
@@ -47264,7 +47265,7 @@
         <v>20</v>
       </c>
       <c r="D1064" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1064" t="s">
         <v>15</v>
@@ -47308,7 +47309,7 @@
         <v>20</v>
       </c>
       <c r="D1065" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1065" t="s">
         <v>15</v>
@@ -47352,7 +47353,7 @@
         <v>20</v>
       </c>
       <c r="D1066" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1066" t="s">
         <v>15</v>
@@ -47396,7 +47397,7 @@
         <v>20</v>
       </c>
       <c r="D1067" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1067" t="s">
         <v>15</v>
@@ -47440,7 +47441,7 @@
         <v>20</v>
       </c>
       <c r="D1068" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1068" t="s">
         <v>15</v>
@@ -47484,7 +47485,7 @@
         <v>20</v>
       </c>
       <c r="D1069" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1069" t="s">
         <v>15</v>
@@ -47528,7 +47529,7 @@
         <v>20</v>
       </c>
       <c r="D1070" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1070" t="s">
         <v>15</v>
@@ -47572,7 +47573,7 @@
         <v>20</v>
       </c>
       <c r="D1071" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1071" t="s">
         <v>15</v>
@@ -47616,7 +47617,7 @@
         <v>20</v>
       </c>
       <c r="D1072" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1072" t="s">
         <v>15</v>
@@ -47660,7 +47661,7 @@
         <v>20</v>
       </c>
       <c r="D1073" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1073" t="s">
         <v>15</v>
@@ -47704,7 +47705,7 @@
         <v>20</v>
       </c>
       <c r="D1074" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1074" t="s">
         <v>15</v>
@@ -47748,7 +47749,7 @@
         <v>20</v>
       </c>
       <c r="D1075" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1075" t="s">
         <v>15</v>
@@ -47792,7 +47793,7 @@
         <v>20</v>
       </c>
       <c r="D1076" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1076" t="s">
         <v>15</v>
@@ -47836,7 +47837,7 @@
         <v>20</v>
       </c>
       <c r="D1077" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1077" t="s">
         <v>15</v>
@@ -47880,7 +47881,7 @@
         <v>20</v>
       </c>
       <c r="D1078" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1078" t="s">
         <v>15</v>
@@ -47924,7 +47925,7 @@
         <v>20</v>
       </c>
       <c r="D1079" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1079" t="s">
         <v>15</v>
@@ -47968,7 +47969,7 @@
         <v>20</v>
       </c>
       <c r="D1080" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1080" t="s">
         <v>15</v>
@@ -48012,7 +48013,7 @@
         <v>20</v>
       </c>
       <c r="D1081" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1081" t="s">
         <v>15</v>
@@ -48056,7 +48057,7 @@
         <v>20</v>
       </c>
       <c r="D1082" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1082" t="s">
         <v>15</v>
@@ -48100,7 +48101,7 @@
         <v>20</v>
       </c>
       <c r="D1083" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1083" t="s">
         <v>15</v>
@@ -48144,7 +48145,7 @@
         <v>20</v>
       </c>
       <c r="D1084" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1084" t="s">
         <v>15</v>
@@ -48188,7 +48189,7 @@
         <v>20</v>
       </c>
       <c r="D1085" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1085" t="s">
         <v>15</v>
@@ -48232,7 +48233,7 @@
         <v>20</v>
       </c>
       <c r="D1086" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1086" t="s">
         <v>15</v>
@@ -48276,7 +48277,7 @@
         <v>20</v>
       </c>
       <c r="D1087" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1087" t="s">
         <v>15</v>
@@ -48320,7 +48321,7 @@
         <v>20</v>
       </c>
       <c r="D1088" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1088" t="s">
         <v>15</v>
@@ -48364,7 +48365,7 @@
         <v>20</v>
       </c>
       <c r="D1089" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1089" t="s">
         <v>15</v>
@@ -48408,7 +48409,7 @@
         <v>20</v>
       </c>
       <c r="D1090" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1090" t="s">
         <v>15</v>
@@ -48452,7 +48453,7 @@
         <v>20</v>
       </c>
       <c r="D1091" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1091" t="s">
         <v>15</v>
@@ -48496,7 +48497,7 @@
         <v>20</v>
       </c>
       <c r="D1092" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1092" t="s">
         <v>15</v>
@@ -48540,7 +48541,7 @@
         <v>20</v>
       </c>
       <c r="D1093" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1093" t="s">
         <v>15</v>
@@ -48584,7 +48585,7 @@
         <v>20</v>
       </c>
       <c r="D1094" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1094" t="s">
         <v>15</v>
@@ -48628,7 +48629,7 @@
         <v>20</v>
       </c>
       <c r="D1095" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1095" t="s">
         <v>15</v>
@@ -48672,7 +48673,7 @@
         <v>20</v>
       </c>
       <c r="D1096" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1096" t="s">
         <v>15</v>
@@ -48716,7 +48717,7 @@
         <v>20</v>
       </c>
       <c r="D1097" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1097" t="s">
         <v>15</v>
@@ -48760,7 +48761,7 @@
         <v>20</v>
       </c>
       <c r="D1098" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1098" t="s">
         <v>15</v>
@@ -48804,7 +48805,7 @@
         <v>20</v>
       </c>
       <c r="D1099" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1099" t="s">
         <v>15</v>
@@ -48848,7 +48849,7 @@
         <v>20</v>
       </c>
       <c r="D1100" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1100" t="s">
         <v>15</v>
@@ -48892,7 +48893,7 @@
         <v>20</v>
       </c>
       <c r="D1101" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1101" t="s">
         <v>15</v>
@@ -48936,7 +48937,7 @@
         <v>20</v>
       </c>
       <c r="D1102" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1102" t="s">
         <v>15</v>
@@ -48980,7 +48981,7 @@
         <v>20</v>
       </c>
       <c r="D1103" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1103" t="s">
         <v>15</v>
@@ -49024,7 +49025,7 @@
         <v>20</v>
       </c>
       <c r="D1104" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1104" t="s">
         <v>15</v>
@@ -49068,7 +49069,7 @@
         <v>20</v>
       </c>
       <c r="D1105" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1105" t="s">
         <v>15</v>
@@ -49112,7 +49113,7 @@
         <v>20</v>
       </c>
       <c r="D1106" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1106" t="s">
         <v>15</v>
@@ -49156,7 +49157,7 @@
         <v>20</v>
       </c>
       <c r="D1107" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1107" t="s">
         <v>15</v>
@@ -49200,7 +49201,7 @@
         <v>20</v>
       </c>
       <c r="D1108" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1108" t="s">
         <v>15</v>
@@ -49244,7 +49245,7 @@
         <v>20</v>
       </c>
       <c r="D1109" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1109" t="s">
         <v>15</v>
@@ -49288,7 +49289,7 @@
         <v>20</v>
       </c>
       <c r="D1110" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1110" t="s">
         <v>15</v>
@@ -49332,7 +49333,7 @@
         <v>20</v>
       </c>
       <c r="D1111" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1111" t="s">
         <v>15</v>
@@ -49376,7 +49377,7 @@
         <v>20</v>
       </c>
       <c r="D1112" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1112" t="s">
         <v>15</v>
@@ -49420,7 +49421,7 @@
         <v>20</v>
       </c>
       <c r="D1113" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1113" t="s">
         <v>15</v>
@@ -49464,7 +49465,7 @@
         <v>20</v>
       </c>
       <c r="D1114" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1114" t="s">
         <v>15</v>
@@ -49508,7 +49509,7 @@
         <v>20</v>
       </c>
       <c r="D1115" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1115" t="s">
         <v>15</v>
@@ -49552,7 +49553,7 @@
         <v>20</v>
       </c>
       <c r="D1116" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1116" t="s">
         <v>15</v>
@@ -49596,7 +49597,7 @@
         <v>20</v>
       </c>
       <c r="D1117" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1117" t="s">
         <v>15</v>
@@ -49640,7 +49641,7 @@
         <v>20</v>
       </c>
       <c r="D1118" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1118" t="s">
         <v>15</v>
@@ -49684,7 +49685,7 @@
         <v>20</v>
       </c>
       <c r="D1119" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1119" t="s">
         <v>15</v>
@@ -49728,7 +49729,7 @@
         <v>20</v>
       </c>
       <c r="D1120" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1120" t="s">
         <v>15</v>
@@ -49772,7 +49773,7 @@
         <v>20</v>
       </c>
       <c r="D1121" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1121" t="s">
         <v>15</v>
@@ -49816,7 +49817,7 @@
         <v>20</v>
       </c>
       <c r="D1122" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1122" t="s">
         <v>15</v>
@@ -49860,7 +49861,7 @@
         <v>20</v>
       </c>
       <c r="D1123" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1123" t="s">
         <v>15</v>
@@ -49904,7 +49905,7 @@
         <v>20</v>
       </c>
       <c r="D1124" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1124" t="s">
         <v>15</v>
@@ -49948,7 +49949,7 @@
         <v>20</v>
       </c>
       <c r="D1125" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1125" t="s">
         <v>15</v>
@@ -49992,7 +49993,7 @@
         <v>20</v>
       </c>
       <c r="D1126" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1126" t="s">
         <v>15</v>
@@ -50036,7 +50037,7 @@
         <v>20</v>
       </c>
       <c r="D1127" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1127" t="s">
         <v>15</v>
@@ -50080,7 +50081,7 @@
         <v>20</v>
       </c>
       <c r="D1128" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1128" t="s">
         <v>15</v>
@@ -50124,7 +50125,7 @@
         <v>20</v>
       </c>
       <c r="D1129" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1129" t="s">
         <v>15</v>
@@ -50168,7 +50169,7 @@
         <v>20</v>
       </c>
       <c r="D1130" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1130" t="s">
         <v>15</v>
@@ -50212,7 +50213,7 @@
         <v>20</v>
       </c>
       <c r="D1131" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1131" t="s">
         <v>15</v>
@@ -50256,7 +50257,7 @@
         <v>20</v>
       </c>
       <c r="D1132" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1132" t="s">
         <v>15</v>
@@ -50300,7 +50301,7 @@
         <v>20</v>
       </c>
       <c r="D1133" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1133" t="s">
         <v>15</v>
@@ -50344,7 +50345,7 @@
         <v>20</v>
       </c>
       <c r="D1134" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1134" t="s">
         <v>15</v>
@@ -50388,7 +50389,7 @@
         <v>20</v>
       </c>
       <c r="D1135" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1135" t="s">
         <v>15</v>
@@ -50432,7 +50433,7 @@
         <v>20</v>
       </c>
       <c r="D1136" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1136" t="s">
         <v>15</v>
@@ -50476,7 +50477,7 @@
         <v>20</v>
       </c>
       <c r="D1137" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1137" t="s">
         <v>15</v>
@@ -50520,7 +50521,7 @@
         <v>20</v>
       </c>
       <c r="D1138" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1138" t="s">
         <v>15</v>
@@ -50564,7 +50565,7 @@
         <v>20</v>
       </c>
       <c r="D1139" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1139" t="s">
         <v>15</v>
@@ -50608,7 +50609,7 @@
         <v>20</v>
       </c>
       <c r="D1140" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1140" t="s">
         <v>15</v>
@@ -50652,7 +50653,7 @@
         <v>20</v>
       </c>
       <c r="D1141" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1141" t="s">
         <v>15</v>
@@ -50696,7 +50697,7 @@
         <v>20</v>
       </c>
       <c r="D1142" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1142" t="s">
         <v>15</v>
@@ -50740,7 +50741,7 @@
         <v>20</v>
       </c>
       <c r="D1143" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1143" t="s">
         <v>15</v>
@@ -50784,7 +50785,7 @@
         <v>20</v>
       </c>
       <c r="D1144" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1144" t="s">
         <v>15</v>
@@ -50828,7 +50829,7 @@
         <v>20</v>
       </c>
       <c r="D1145" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1145" t="s">
         <v>15</v>
@@ -50872,7 +50873,7 @@
         <v>20</v>
       </c>
       <c r="D1146" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1146" t="s">
         <v>15</v>
@@ -50916,7 +50917,7 @@
         <v>20</v>
       </c>
       <c r="D1147" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1147" t="s">
         <v>15</v>
@@ -50960,7 +50961,7 @@
         <v>20</v>
       </c>
       <c r="D1148" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1148" t="s">
         <v>15</v>
@@ -51004,7 +51005,7 @@
         <v>20</v>
       </c>
       <c r="D1149" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1149" t="s">
         <v>15</v>
@@ -51048,7 +51049,7 @@
         <v>20</v>
       </c>
       <c r="D1150" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1150" t="s">
         <v>15</v>
@@ -51092,7 +51093,7 @@
         <v>20</v>
       </c>
       <c r="D1151" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1151" t="s">
         <v>15</v>
@@ -51136,7 +51137,7 @@
         <v>20</v>
       </c>
       <c r="D1152" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1152" t="s">
         <v>15</v>
@@ -51180,7 +51181,7 @@
         <v>20</v>
       </c>
       <c r="D1153" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1153" t="s">
         <v>15</v>
@@ -51224,7 +51225,7 @@
         <v>20</v>
       </c>
       <c r="D1154" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1154" t="s">
         <v>15</v>
@@ -51268,7 +51269,7 @@
         <v>20</v>
       </c>
       <c r="D1155" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1155" t="s">
         <v>15</v>
@@ -51312,7 +51313,7 @@
         <v>20</v>
       </c>
       <c r="D1156" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1156" t="s">
         <v>15</v>
@@ -51356,7 +51357,7 @@
         <v>20</v>
       </c>
       <c r="D1157" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1157" t="s">
         <v>15</v>
@@ -51400,7 +51401,7 @@
         <v>20</v>
       </c>
       <c r="D1158" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1158" t="s">
         <v>15</v>
@@ -51444,7 +51445,7 @@
         <v>20</v>
       </c>
       <c r="D1159" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1159" t="s">
         <v>15</v>
@@ -51488,7 +51489,7 @@
         <v>20</v>
       </c>
       <c r="D1160" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1160" t="s">
         <v>15</v>
@@ -51532,7 +51533,7 @@
         <v>20</v>
       </c>
       <c r="D1161" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1161" t="s">
         <v>15</v>
@@ -51576,7 +51577,7 @@
         <v>20</v>
       </c>
       <c r="D1162" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1162" t="s">
         <v>15</v>
@@ -51620,7 +51621,7 @@
         <v>20</v>
       </c>
       <c r="D1163" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1163" t="s">
         <v>15</v>
@@ -51664,7 +51665,7 @@
         <v>20</v>
       </c>
       <c r="D1164" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1164" t="s">
         <v>15</v>
@@ -51708,7 +51709,7 @@
         <v>20</v>
       </c>
       <c r="D1165" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1165" t="s">
         <v>15</v>
@@ -51752,7 +51753,7 @@
         <v>20</v>
       </c>
       <c r="D1166" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1166" t="s">
         <v>15</v>
@@ -51796,7 +51797,7 @@
         <v>20</v>
       </c>
       <c r="D1167" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1167" t="s">
         <v>15</v>
@@ -51840,7 +51841,7 @@
         <v>20</v>
       </c>
       <c r="D1168" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1168" t="s">
         <v>15</v>
@@ -51884,7 +51885,7 @@
         <v>20</v>
       </c>
       <c r="D1169" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1169" t="s">
         <v>15</v>
@@ -51928,7 +51929,7 @@
         <v>20</v>
       </c>
       <c r="D1170" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1170" t="s">
         <v>15</v>
@@ -51972,7 +51973,7 @@
         <v>20</v>
       </c>
       <c r="D1171" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1171" t="s">
         <v>15</v>
@@ -52016,7 +52017,7 @@
         <v>20</v>
       </c>
       <c r="D1172" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1172" t="s">
         <v>15</v>
@@ -52060,7 +52061,7 @@
         <v>20</v>
       </c>
       <c r="D1173" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1173" t="s">
         <v>15</v>
@@ -52104,7 +52105,7 @@
         <v>20</v>
       </c>
       <c r="D1174" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1174" t="s">
         <v>15</v>
@@ -52148,7 +52149,7 @@
         <v>20</v>
       </c>
       <c r="D1175" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1175" t="s">
         <v>15</v>
@@ -52192,7 +52193,7 @@
         <v>20</v>
       </c>
       <c r="D1176" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1176" t="s">
         <v>15</v>
@@ -52236,7 +52237,7 @@
         <v>20</v>
       </c>
       <c r="D1177" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1177" t="s">
         <v>15</v>
@@ -52280,7 +52281,7 @@
         <v>20</v>
       </c>
       <c r="D1178" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1178" t="s">
         <v>15</v>
@@ -52324,7 +52325,7 @@
         <v>20</v>
       </c>
       <c r="D1179" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1179" t="s">
         <v>15</v>
@@ -52368,7 +52369,7 @@
         <v>20</v>
       </c>
       <c r="D1180" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1180" t="s">
         <v>15</v>
@@ -52412,7 +52413,7 @@
         <v>20</v>
       </c>
       <c r="D1181" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1181" t="s">
         <v>15</v>
@@ -52456,7 +52457,7 @@
         <v>20</v>
       </c>
       <c r="D1182" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1182" t="s">
         <v>15</v>
@@ -52500,7 +52501,7 @@
         <v>20</v>
       </c>
       <c r="D1183" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1183" t="s">
         <v>15</v>
@@ -52544,7 +52545,7 @@
         <v>20</v>
       </c>
       <c r="D1184" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1184" t="s">
         <v>15</v>
@@ -52588,7 +52589,7 @@
         <v>20</v>
       </c>
       <c r="D1185" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1185" t="s">
         <v>15</v>
@@ -52632,7 +52633,7 @@
         <v>20</v>
       </c>
       <c r="D1186" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1186" t="s">
         <v>15</v>
@@ -52676,7 +52677,7 @@
         <v>20</v>
       </c>
       <c r="D1187" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1187" t="s">
         <v>15</v>
@@ -52720,7 +52721,7 @@
         <v>20</v>
       </c>
       <c r="D1188" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1188" t="s">
         <v>15</v>
@@ -52764,7 +52765,7 @@
         <v>20</v>
       </c>
       <c r="D1189" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1189" t="s">
         <v>15</v>
@@ -52808,7 +52809,7 @@
         <v>20</v>
       </c>
       <c r="D1190" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1190" t="s">
         <v>15</v>
@@ -52852,7 +52853,7 @@
         <v>20</v>
       </c>
       <c r="D1191" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1191" t="s">
         <v>15</v>
@@ -52896,7 +52897,7 @@
         <v>20</v>
       </c>
       <c r="D1192" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1192" t="s">
         <v>15</v>
@@ -52940,7 +52941,7 @@
         <v>20</v>
       </c>
       <c r="D1193" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1193" t="s">
         <v>15</v>
@@ -52984,7 +52985,7 @@
         <v>20</v>
       </c>
       <c r="D1194" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1194" t="s">
         <v>15</v>
@@ -53028,7 +53029,7 @@
         <v>20</v>
       </c>
       <c r="D1195" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1195" t="s">
         <v>15</v>
@@ -53072,7 +53073,7 @@
         <v>20</v>
       </c>
       <c r="D1196" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1196" t="s">
         <v>15</v>
@@ -53116,7 +53117,7 @@
         <v>20</v>
       </c>
       <c r="D1197" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1197" t="s">
         <v>15</v>
@@ -53160,7 +53161,7 @@
         <v>20</v>
       </c>
       <c r="D1198" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1198" t="s">
         <v>15</v>
@@ -53204,7 +53205,7 @@
         <v>20</v>
       </c>
       <c r="D1199" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1199" t="s">
         <v>15</v>
@@ -53248,7 +53249,7 @@
         <v>20</v>
       </c>
       <c r="D1200" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1200" t="s">
         <v>15</v>
@@ -53292,7 +53293,7 @@
         <v>20</v>
       </c>
       <c r="D1201" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1201" t="s">
         <v>15</v>
@@ -53336,7 +53337,7 @@
         <v>20</v>
       </c>
       <c r="D1202" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1202" t="s">
         <v>15</v>
@@ -53380,7 +53381,7 @@
         <v>20</v>
       </c>
       <c r="D1203" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1203" t="s">
         <v>15</v>
@@ -53424,7 +53425,7 @@
         <v>20</v>
       </c>
       <c r="D1204" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1204" t="s">
         <v>15</v>
@@ -53468,7 +53469,7 @@
         <v>20</v>
       </c>
       <c r="D1205" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1205" t="s">
         <v>15</v>
@@ -53512,7 +53513,7 @@
         <v>20</v>
       </c>
       <c r="D1206" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1206" t="s">
         <v>15</v>
@@ -53556,7 +53557,7 @@
         <v>20</v>
       </c>
       <c r="D1207" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1207" t="s">
         <v>15</v>
@@ -53600,7 +53601,7 @@
         <v>20</v>
       </c>
       <c r="D1208" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1208" t="s">
         <v>15</v>
@@ -53644,7 +53645,7 @@
         <v>20</v>
       </c>
       <c r="D1209" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1209" t="s">
         <v>15</v>
@@ -53688,7 +53689,7 @@
         <v>20</v>
       </c>
       <c r="D1210" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1210" t="s">
         <v>15</v>
@@ -53732,7 +53733,7 @@
         <v>20</v>
       </c>
       <c r="D1211" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1211" t="s">
         <v>15</v>
@@ -53776,7 +53777,7 @@
         <v>20</v>
       </c>
       <c r="D1212" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1212" t="s">
         <v>15</v>
@@ -53820,7 +53821,7 @@
         <v>20</v>
       </c>
       <c r="D1213" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1213" t="s">
         <v>15</v>
@@ -53864,7 +53865,7 @@
         <v>20</v>
       </c>
       <c r="D1214" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1214" t="s">
         <v>15</v>
@@ -53908,7 +53909,7 @@
         <v>20</v>
       </c>
       <c r="D1215" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1215" t="s">
         <v>15</v>
@@ -53952,7 +53953,7 @@
         <v>20</v>
       </c>
       <c r="D1216" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1216" t="s">
         <v>15</v>
@@ -53996,7 +53997,7 @@
         <v>20</v>
       </c>
       <c r="D1217" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1217" t="s">
         <v>15</v>
@@ -54040,7 +54041,7 @@
         <v>20</v>
       </c>
       <c r="D1218" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1218" t="s">
         <v>15</v>
@@ -54084,7 +54085,7 @@
         <v>20</v>
       </c>
       <c r="D1219" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1219" t="s">
         <v>15</v>
@@ -54128,7 +54129,7 @@
         <v>20</v>
       </c>
       <c r="D1220" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1220" t="s">
         <v>15</v>
@@ -54172,7 +54173,7 @@
         <v>20</v>
       </c>
       <c r="D1221" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1221" t="s">
         <v>15</v>
@@ -54216,7 +54217,7 @@
         <v>20</v>
       </c>
       <c r="D1222" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1222" t="s">
         <v>15</v>
@@ -54260,7 +54261,7 @@
         <v>20</v>
       </c>
       <c r="D1223" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1223" t="s">
         <v>15</v>
@@ -54304,7 +54305,7 @@
         <v>20</v>
       </c>
       <c r="D1224" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1224" t="s">
         <v>15</v>
@@ -54348,7 +54349,7 @@
         <v>20</v>
       </c>
       <c r="D1225" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1225" t="s">
         <v>15</v>
@@ -54392,7 +54393,7 @@
         <v>20</v>
       </c>
       <c r="D1226" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1226" t="s">
         <v>15</v>
@@ -54436,7 +54437,7 @@
         <v>20</v>
       </c>
       <c r="D1227" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1227" t="s">
         <v>15</v>
@@ -54480,7 +54481,7 @@
         <v>20</v>
       </c>
       <c r="D1228" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1228" t="s">
         <v>15</v>
@@ -54524,7 +54525,7 @@
         <v>20</v>
       </c>
       <c r="D1229" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1229" t="s">
         <v>15</v>
@@ -54568,7 +54569,7 @@
         <v>20</v>
       </c>
       <c r="D1230" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1230" t="s">
         <v>15</v>
@@ -54612,7 +54613,7 @@
         <v>20</v>
       </c>
       <c r="D1231" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1231" t="s">
         <v>15</v>
@@ -54656,7 +54657,7 @@
         <v>20</v>
       </c>
       <c r="D1232" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1232" t="s">
         <v>15</v>
@@ -54700,7 +54701,7 @@
         <v>20</v>
       </c>
       <c r="D1233" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1233" t="s">
         <v>15</v>
@@ -54744,7 +54745,7 @@
         <v>20</v>
       </c>
       <c r="D1234" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1234" t="s">
         <v>15</v>
@@ -54788,7 +54789,7 @@
         <v>20</v>
       </c>
       <c r="D1235" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1235" t="s">
         <v>15</v>
@@ -54832,7 +54833,7 @@
         <v>20</v>
       </c>
       <c r="D1236" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1236" t="s">
         <v>15</v>
@@ -54876,7 +54877,7 @@
         <v>20</v>
       </c>
       <c r="D1237" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1237" t="s">
         <v>16</v>
@@ -54920,7 +54921,7 @@
         <v>20</v>
       </c>
       <c r="D1238" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1238" t="s">
         <v>16</v>
@@ -54964,7 +54965,7 @@
         <v>20</v>
       </c>
       <c r="D1239" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1239" t="s">
         <v>16</v>
@@ -55008,7 +55009,7 @@
         <v>20</v>
       </c>
       <c r="D1240" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1240" t="s">
         <v>16</v>
@@ -55052,7 +55053,7 @@
         <v>20</v>
       </c>
       <c r="D1241" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1241" t="s">
         <v>16</v>
@@ -55096,7 +55097,7 @@
         <v>20</v>
       </c>
       <c r="D1242" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1242" t="s">
         <v>16</v>
@@ -55140,7 +55141,7 @@
         <v>20</v>
       </c>
       <c r="D1243" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1243" t="s">
         <v>16</v>
@@ -55184,7 +55185,7 @@
         <v>20</v>
       </c>
       <c r="D1244" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1244" t="s">
         <v>16</v>
@@ -55228,7 +55229,7 @@
         <v>20</v>
       </c>
       <c r="D1245" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1245" t="s">
         <v>16</v>
@@ -55272,7 +55273,7 @@
         <v>20</v>
       </c>
       <c r="D1246" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1246" t="s">
         <v>16</v>
@@ -55316,7 +55317,7 @@
         <v>20</v>
       </c>
       <c r="D1247" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1247" t="s">
         <v>16</v>
@@ -55360,7 +55361,7 @@
         <v>20</v>
       </c>
       <c r="D1248" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1248" t="s">
         <v>16</v>
@@ -55404,7 +55405,7 @@
         <v>20</v>
       </c>
       <c r="D1249" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1249" t="s">
         <v>16</v>
@@ -55448,7 +55449,7 @@
         <v>20</v>
       </c>
       <c r="D1250" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1250" t="s">
         <v>16</v>
@@ -55492,7 +55493,7 @@
         <v>20</v>
       </c>
       <c r="D1251" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1251" t="s">
         <v>16</v>
@@ -55536,7 +55537,7 @@
         <v>20</v>
       </c>
       <c r="D1252" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1252" t="s">
         <v>16</v>
@@ -55580,7 +55581,7 @@
         <v>20</v>
       </c>
       <c r="D1253" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1253" t="s">
         <v>16</v>
@@ -55624,7 +55625,7 @@
         <v>20</v>
       </c>
       <c r="D1254" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1254" t="s">
         <v>16</v>
@@ -55668,7 +55669,7 @@
         <v>20</v>
       </c>
       <c r="D1255" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1255" t="s">
         <v>16</v>
@@ -55712,7 +55713,7 @@
         <v>20</v>
       </c>
       <c r="D1256" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1256" t="s">
         <v>16</v>
@@ -55756,7 +55757,7 @@
         <v>20</v>
       </c>
       <c r="D1257" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1257" t="s">
         <v>16</v>
@@ -55800,7 +55801,7 @@
         <v>20</v>
       </c>
       <c r="D1258" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1258" t="s">
         <v>16</v>
@@ -55844,7 +55845,7 @@
         <v>20</v>
       </c>
       <c r="D1259" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1259" t="s">
         <v>16</v>
@@ -55888,7 +55889,7 @@
         <v>20</v>
       </c>
       <c r="D1260" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1260" t="s">
         <v>16</v>
@@ -55932,7 +55933,7 @@
         <v>20</v>
       </c>
       <c r="D1261" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1261" t="s">
         <v>16</v>
@@ -55976,7 +55977,7 @@
         <v>20</v>
       </c>
       <c r="D1262" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1262" t="s">
         <v>16</v>
@@ -56020,7 +56021,7 @@
         <v>20</v>
       </c>
       <c r="D1263" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1263" t="s">
         <v>16</v>
@@ -56064,7 +56065,7 @@
         <v>20</v>
       </c>
       <c r="D1264" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1264" t="s">
         <v>16</v>
@@ -56108,7 +56109,7 @@
         <v>20</v>
       </c>
       <c r="D1265" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1265" t="s">
         <v>16</v>
@@ -56152,7 +56153,7 @@
         <v>20</v>
       </c>
       <c r="D1266" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1266" t="s">
         <v>16</v>
@@ -56196,7 +56197,7 @@
         <v>20</v>
       </c>
       <c r="D1267" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1267" t="s">
         <v>16</v>
@@ -56240,7 +56241,7 @@
         <v>20</v>
       </c>
       <c r="D1268" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1268" t="s">
         <v>16</v>
@@ -56284,7 +56285,7 @@
         <v>20</v>
       </c>
       <c r="D1269" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1269" t="s">
         <v>16</v>
@@ -56328,7 +56329,7 @@
         <v>20</v>
       </c>
       <c r="D1270" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1270" t="s">
         <v>16</v>
@@ -56372,7 +56373,7 @@
         <v>20</v>
       </c>
       <c r="D1271" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1271" t="s">
         <v>16</v>
@@ -56416,7 +56417,7 @@
         <v>20</v>
       </c>
       <c r="D1272" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1272" t="s">
         <v>16</v>
@@ -56460,7 +56461,7 @@
         <v>20</v>
       </c>
       <c r="D1273" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1273" t="s">
         <v>16</v>
@@ -56504,7 +56505,7 @@
         <v>20</v>
       </c>
       <c r="D1274" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1274" t="s">
         <v>16</v>
@@ -56548,7 +56549,7 @@
         <v>20</v>
       </c>
       <c r="D1275" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1275" t="s">
         <v>16</v>
@@ -56592,7 +56593,7 @@
         <v>20</v>
       </c>
       <c r="D1276" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1276" t="s">
         <v>16</v>
@@ -56636,7 +56637,7 @@
         <v>20</v>
       </c>
       <c r="D1277" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1277" t="s">
         <v>16</v>
@@ -56680,7 +56681,7 @@
         <v>20</v>
       </c>
       <c r="D1278" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1278" t="s">
         <v>16</v>
@@ -56724,7 +56725,7 @@
         <v>20</v>
       </c>
       <c r="D1279" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1279" t="s">
         <v>16</v>
@@ -56768,7 +56769,7 @@
         <v>20</v>
       </c>
       <c r="D1280" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1280" t="s">
         <v>16</v>
@@ -56812,7 +56813,7 @@
         <v>20</v>
       </c>
       <c r="D1281" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1281" t="s">
         <v>16</v>
@@ -56856,7 +56857,7 @@
         <v>20</v>
       </c>
       <c r="D1282" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1282" t="s">
         <v>16</v>
@@ -56900,7 +56901,7 @@
         <v>20</v>
       </c>
       <c r="D1283" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1283" t="s">
         <v>16</v>
@@ -56944,7 +56945,7 @@
         <v>20</v>
       </c>
       <c r="D1284" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1284" t="s">
         <v>16</v>
@@ -56988,7 +56989,7 @@
         <v>20</v>
       </c>
       <c r="D1285" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1285" t="s">
         <v>16</v>
@@ -57032,7 +57033,7 @@
         <v>20</v>
       </c>
       <c r="D1286" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1286" t="s">
         <v>16</v>
@@ -57076,7 +57077,7 @@
         <v>20</v>
       </c>
       <c r="D1287" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1287" t="s">
         <v>16</v>
@@ -57120,7 +57121,7 @@
         <v>20</v>
       </c>
       <c r="D1288" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1288" t="s">
         <v>16</v>
@@ -57164,7 +57165,7 @@
         <v>20</v>
       </c>
       <c r="D1289" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1289" t="s">
         <v>16</v>
@@ -57208,7 +57209,7 @@
         <v>20</v>
       </c>
       <c r="D1290" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1290" t="s">
         <v>16</v>
@@ -57252,7 +57253,7 @@
         <v>20</v>
       </c>
       <c r="D1291" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1291" t="s">
         <v>16</v>
@@ -57296,7 +57297,7 @@
         <v>20</v>
       </c>
       <c r="D1292" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1292" t="s">
         <v>16</v>
@@ -57340,7 +57341,7 @@
         <v>20</v>
       </c>
       <c r="D1293" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1293" t="s">
         <v>16</v>
@@ -57384,7 +57385,7 @@
         <v>20</v>
       </c>
       <c r="D1294" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1294" t="s">
         <v>16</v>
@@ -57428,7 +57429,7 @@
         <v>20</v>
       </c>
       <c r="D1295" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1295" t="s">
         <v>16</v>
@@ -57472,7 +57473,7 @@
         <v>20</v>
       </c>
       <c r="D1296" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1296" t="s">
         <v>16</v>
@@ -57516,7 +57517,7 @@
         <v>20</v>
       </c>
       <c r="D1297" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1297" t="s">
         <v>16</v>
@@ -57560,7 +57561,7 @@
         <v>20</v>
       </c>
       <c r="D1298" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1298" t="s">
         <v>16</v>
@@ -57604,7 +57605,7 @@
         <v>20</v>
       </c>
       <c r="D1299" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1299" t="s">
         <v>16</v>
@@ -57648,7 +57649,7 @@
         <v>20</v>
       </c>
       <c r="D1300" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1300" t="s">
         <v>16</v>
@@ -57692,7 +57693,7 @@
         <v>20</v>
       </c>
       <c r="D1301" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1301" t="s">
         <v>16</v>
@@ -57736,7 +57737,7 @@
         <v>20</v>
       </c>
       <c r="D1302" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1302" t="s">
         <v>16</v>
@@ -57780,7 +57781,7 @@
         <v>20</v>
       </c>
       <c r="D1303" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1303" t="s">
         <v>16</v>
@@ -57824,7 +57825,7 @@
         <v>20</v>
       </c>
       <c r="D1304" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1304" t="s">
         <v>16</v>
@@ -57868,7 +57869,7 @@
         <v>20</v>
       </c>
       <c r="D1305" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1305" t="s">
         <v>16</v>
@@ -57912,7 +57913,7 @@
         <v>20</v>
       </c>
       <c r="D1306" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1306" t="s">
         <v>16</v>
@@ -57956,7 +57957,7 @@
         <v>20</v>
       </c>
       <c r="D1307" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1307" t="s">
         <v>16</v>
@@ -58000,7 +58001,7 @@
         <v>20</v>
       </c>
       <c r="D1308" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1308" t="s">
         <v>16</v>
@@ -58044,7 +58045,7 @@
         <v>20</v>
       </c>
       <c r="D1309" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1309" t="s">
         <v>16</v>
@@ -58088,7 +58089,7 @@
         <v>20</v>
       </c>
       <c r="D1310" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1310" t="s">
         <v>16</v>
@@ -58132,7 +58133,7 @@
         <v>20</v>
       </c>
       <c r="D1311" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1311" t="s">
         <v>16</v>
@@ -58176,7 +58177,7 @@
         <v>20</v>
       </c>
       <c r="D1312" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1312" t="s">
         <v>16</v>
@@ -58220,7 +58221,7 @@
         <v>20</v>
       </c>
       <c r="D1313" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1313" t="s">
         <v>16</v>
@@ -58264,7 +58265,7 @@
         <v>20</v>
       </c>
       <c r="D1314" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1314" t="s">
         <v>16</v>
@@ -58308,7 +58309,7 @@
         <v>20</v>
       </c>
       <c r="D1315" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1315" t="s">
         <v>16</v>
@@ -58352,7 +58353,7 @@
         <v>20</v>
       </c>
       <c r="D1316" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1316" t="s">
         <v>16</v>
@@ -58396,7 +58397,7 @@
         <v>20</v>
       </c>
       <c r="D1317" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1317" t="s">
         <v>16</v>
@@ -58440,7 +58441,7 @@
         <v>20</v>
       </c>
       <c r="D1318" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1318" t="s">
         <v>16</v>
@@ -58484,7 +58485,7 @@
         <v>20</v>
       </c>
       <c r="D1319" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1319" t="s">
         <v>16</v>
@@ -58528,7 +58529,7 @@
         <v>20</v>
       </c>
       <c r="D1320" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1320" t="s">
         <v>16</v>
@@ -58572,7 +58573,7 @@
         <v>20</v>
       </c>
       <c r="D1321" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1321" t="s">
         <v>16</v>
@@ -58616,7 +58617,7 @@
         <v>20</v>
       </c>
       <c r="D1322" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1322" t="s">
         <v>16</v>
@@ -58660,7 +58661,7 @@
         <v>20</v>
       </c>
       <c r="D1323" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1323" t="s">
         <v>16</v>
@@ -58704,7 +58705,7 @@
         <v>20</v>
       </c>
       <c r="D1324" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1324" t="s">
         <v>16</v>
@@ -58748,7 +58749,7 @@
         <v>20</v>
       </c>
       <c r="D1325" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1325" t="s">
         <v>16</v>
@@ -58792,7 +58793,7 @@
         <v>20</v>
       </c>
       <c r="D1326" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1326" t="s">
         <v>16</v>
@@ -58836,7 +58837,7 @@
         <v>20</v>
       </c>
       <c r="D1327" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1327" t="s">
         <v>16</v>
@@ -58880,7 +58881,7 @@
         <v>20</v>
       </c>
       <c r="D1328" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1328" t="s">
         <v>16</v>
@@ -58924,7 +58925,7 @@
         <v>20</v>
       </c>
       <c r="D1329" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1329" t="s">
         <v>16</v>
@@ -58968,7 +58969,7 @@
         <v>20</v>
       </c>
       <c r="D1330" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1330" t="s">
         <v>16</v>
@@ -59012,7 +59013,7 @@
         <v>20</v>
       </c>
       <c r="D1331" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1331" t="s">
         <v>16</v>
@@ -59056,7 +59057,7 @@
         <v>20</v>
       </c>
       <c r="D1332" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1332" t="s">
         <v>16</v>
@@ -59100,7 +59101,7 @@
         <v>20</v>
       </c>
       <c r="D1333" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1333" t="s">
         <v>16</v>
@@ -59144,7 +59145,7 @@
         <v>20</v>
       </c>
       <c r="D1334" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1334" t="s">
         <v>16</v>
@@ -59188,7 +59189,7 @@
         <v>20</v>
       </c>
       <c r="D1335" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1335" t="s">
         <v>16</v>
@@ -59232,7 +59233,7 @@
         <v>20</v>
       </c>
       <c r="D1336" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1336" t="s">
         <v>16</v>
@@ -59276,7 +59277,7 @@
         <v>20</v>
       </c>
       <c r="D1337" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1337" t="s">
         <v>16</v>
@@ -59320,7 +59321,7 @@
         <v>20</v>
       </c>
       <c r="D1338" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1338" t="s">
         <v>16</v>
@@ -59364,7 +59365,7 @@
         <v>20</v>
       </c>
       <c r="D1339" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1339" t="s">
         <v>16</v>
@@ -59408,7 +59409,7 @@
         <v>20</v>
       </c>
       <c r="D1340" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1340" t="s">
         <v>16</v>
@@ -59452,7 +59453,7 @@
         <v>20</v>
       </c>
       <c r="D1341" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1341" t="s">
         <v>16</v>
@@ -59496,7 +59497,7 @@
         <v>20</v>
       </c>
       <c r="D1342" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1342" t="s">
         <v>16</v>
@@ -59540,7 +59541,7 @@
         <v>20</v>
       </c>
       <c r="D1343" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1343" t="s">
         <v>16</v>
@@ -59584,7 +59585,7 @@
         <v>20</v>
       </c>
       <c r="D1344" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1344" t="s">
         <v>16</v>
@@ -59628,7 +59629,7 @@
         <v>20</v>
       </c>
       <c r="D1345" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1345" t="s">
         <v>16</v>
@@ -59672,7 +59673,7 @@
         <v>20</v>
       </c>
       <c r="D1346" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1346" t="s">
         <v>16</v>
@@ -59716,7 +59717,7 @@
         <v>20</v>
       </c>
       <c r="D1347" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1347" t="s">
         <v>16</v>
@@ -59760,7 +59761,7 @@
         <v>20</v>
       </c>
       <c r="D1348" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1348" t="s">
         <v>16</v>
@@ -59804,7 +59805,7 @@
         <v>20</v>
       </c>
       <c r="D1349" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1349" t="s">
         <v>16</v>
@@ -59848,7 +59849,7 @@
         <v>20</v>
       </c>
       <c r="D1350" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1350" t="s">
         <v>16</v>
@@ -59892,7 +59893,7 @@
         <v>20</v>
       </c>
       <c r="D1351" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1351" t="s">
         <v>16</v>
@@ -59936,7 +59937,7 @@
         <v>20</v>
       </c>
       <c r="D1352" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1352" t="s">
         <v>16</v>
@@ -59980,7 +59981,7 @@
         <v>20</v>
       </c>
       <c r="D1353" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1353" t="s">
         <v>16</v>
@@ -60024,7 +60025,7 @@
         <v>20</v>
       </c>
       <c r="D1354" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1354" t="s">
         <v>16</v>
@@ -60068,7 +60069,7 @@
         <v>20</v>
       </c>
       <c r="D1355" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1355" t="s">
         <v>16</v>
@@ -60112,7 +60113,7 @@
         <v>20</v>
       </c>
       <c r="D1356" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1356" t="s">
         <v>16</v>
@@ -60156,7 +60157,7 @@
         <v>20</v>
       </c>
       <c r="D1357" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1357" t="s">
         <v>16</v>
@@ -60200,7 +60201,7 @@
         <v>20</v>
       </c>
       <c r="D1358" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1358" t="s">
         <v>16</v>
@@ -60244,7 +60245,7 @@
         <v>20</v>
       </c>
       <c r="D1359" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1359" t="s">
         <v>16</v>
@@ -60288,7 +60289,7 @@
         <v>20</v>
       </c>
       <c r="D1360" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1360" t="s">
         <v>16</v>
@@ -60332,7 +60333,7 @@
         <v>20</v>
       </c>
       <c r="D1361" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1361" t="s">
         <v>16</v>
@@ -60376,7 +60377,7 @@
         <v>20</v>
       </c>
       <c r="D1362" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1362" t="s">
         <v>16</v>
@@ -60420,7 +60421,7 @@
         <v>20</v>
       </c>
       <c r="D1363" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1363" t="s">
         <v>16</v>
@@ -60464,7 +60465,7 @@
         <v>20</v>
       </c>
       <c r="D1364" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1364" t="s">
         <v>16</v>
@@ -60508,7 +60509,7 @@
         <v>20</v>
       </c>
       <c r="D1365" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1365" t="s">
         <v>16</v>
@@ -60552,7 +60553,7 @@
         <v>20</v>
       </c>
       <c r="D1366" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1366" t="s">
         <v>16</v>
@@ -60596,7 +60597,7 @@
         <v>20</v>
       </c>
       <c r="D1367" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1367" t="s">
         <v>16</v>
@@ -60640,7 +60641,7 @@
         <v>20</v>
       </c>
       <c r="D1368" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1368" t="s">
         <v>16</v>
@@ -60684,7 +60685,7 @@
         <v>20</v>
       </c>
       <c r="D1369" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1369" t="s">
         <v>16</v>
@@ -60728,7 +60729,7 @@
         <v>20</v>
       </c>
       <c r="D1370" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1370" t="s">
         <v>16</v>
@@ -60772,7 +60773,7 @@
         <v>20</v>
       </c>
       <c r="D1371" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1371" t="s">
         <v>16</v>
@@ -60816,7 +60817,7 @@
         <v>20</v>
       </c>
       <c r="D1372" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1372" t="s">
         <v>16</v>
@@ -60860,7 +60861,7 @@
         <v>20</v>
       </c>
       <c r="D1373" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1373" t="s">
         <v>16</v>
@@ -60904,7 +60905,7 @@
         <v>20</v>
       </c>
       <c r="D1374" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1374" t="s">
         <v>16</v>
@@ -60948,7 +60949,7 @@
         <v>20</v>
       </c>
       <c r="D1375" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1375" t="s">
         <v>16</v>
@@ -60992,7 +60993,7 @@
         <v>20</v>
       </c>
       <c r="D1376" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1376" t="s">
         <v>16</v>
@@ -61036,7 +61037,7 @@
         <v>20</v>
       </c>
       <c r="D1377" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1377" t="s">
         <v>16</v>
@@ -61080,7 +61081,7 @@
         <v>20</v>
       </c>
       <c r="D1378" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1378" t="s">
         <v>16</v>
@@ -61124,7 +61125,7 @@
         <v>20</v>
       </c>
       <c r="D1379" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1379" t="s">
         <v>16</v>
@@ -61168,7 +61169,7 @@
         <v>20</v>
       </c>
       <c r="D1380" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1380" t="s">
         <v>16</v>
@@ -61212,7 +61213,7 @@
         <v>20</v>
       </c>
       <c r="D1381" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1381" t="s">
         <v>16</v>
@@ -61256,7 +61257,7 @@
         <v>20</v>
       </c>
       <c r="D1382" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1382" t="s">
         <v>16</v>
@@ -61300,7 +61301,7 @@
         <v>20</v>
       </c>
       <c r="D1383" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1383" t="s">
         <v>16</v>
@@ -61344,7 +61345,7 @@
         <v>20</v>
       </c>
       <c r="D1384" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1384" t="s">
         <v>16</v>
@@ -61388,7 +61389,7 @@
         <v>20</v>
       </c>
       <c r="D1385" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1385" t="s">
         <v>16</v>
@@ -61432,7 +61433,7 @@
         <v>20</v>
       </c>
       <c r="D1386" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1386" t="s">
         <v>16</v>
@@ -61476,7 +61477,7 @@
         <v>20</v>
       </c>
       <c r="D1387" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1387" t="s">
         <v>16</v>
@@ -61520,7 +61521,7 @@
         <v>20</v>
       </c>
       <c r="D1388" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1388" t="s">
         <v>16</v>
@@ -61564,7 +61565,7 @@
         <v>20</v>
       </c>
       <c r="D1389" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1389" t="s">
         <v>16</v>
@@ -61608,7 +61609,7 @@
         <v>20</v>
       </c>
       <c r="D1390" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1390" t="s">
         <v>16</v>
@@ -61652,7 +61653,7 @@
         <v>20</v>
       </c>
       <c r="D1391" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1391" t="s">
         <v>16</v>
@@ -61696,7 +61697,7 @@
         <v>20</v>
       </c>
       <c r="D1392" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1392" t="s">
         <v>16</v>
@@ -61740,7 +61741,7 @@
         <v>20</v>
       </c>
       <c r="D1393" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1393" t="s">
         <v>16</v>
@@ -61784,7 +61785,7 @@
         <v>20</v>
       </c>
       <c r="D1394" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1394" t="s">
         <v>16</v>
@@ -61828,7 +61829,7 @@
         <v>20</v>
       </c>
       <c r="D1395" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1395" t="s">
         <v>16</v>
@@ -61872,7 +61873,7 @@
         <v>20</v>
       </c>
       <c r="D1396" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1396" t="s">
         <v>16</v>
@@ -61916,7 +61917,7 @@
         <v>20</v>
       </c>
       <c r="D1397" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1397" t="s">
         <v>16</v>
@@ -61960,7 +61961,7 @@
         <v>20</v>
       </c>
       <c r="D1398" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1398" t="s">
         <v>16</v>
@@ -62004,7 +62005,7 @@
         <v>20</v>
       </c>
       <c r="D1399" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1399" t="s">
         <v>16</v>
@@ -62048,7 +62049,7 @@
         <v>20</v>
       </c>
       <c r="D1400" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1400" t="s">
         <v>16</v>
@@ -62092,7 +62093,7 @@
         <v>20</v>
       </c>
       <c r="D1401" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1401" t="s">
         <v>16</v>
@@ -62136,7 +62137,7 @@
         <v>20</v>
       </c>
       <c r="D1402" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1402" t="s">
         <v>16</v>
@@ -62180,7 +62181,7 @@
         <v>20</v>
       </c>
       <c r="D1403" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1403" t="s">
         <v>16</v>
@@ -62224,7 +62225,7 @@
         <v>20</v>
       </c>
       <c r="D1404" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1404" t="s">
         <v>16</v>
@@ -62268,7 +62269,7 @@
         <v>20</v>
       </c>
       <c r="D1405" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1405" t="s">
         <v>16</v>
@@ -62312,7 +62313,7 @@
         <v>20</v>
       </c>
       <c r="D1406" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1406" t="s">
         <v>16</v>
@@ -62356,7 +62357,7 @@
         <v>20</v>
       </c>
       <c r="D1407" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1407" t="s">
         <v>16</v>
@@ -62400,7 +62401,7 @@
         <v>20</v>
       </c>
       <c r="D1408" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1408" t="s">
         <v>16</v>
@@ -62444,7 +62445,7 @@
         <v>20</v>
       </c>
       <c r="D1409" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1409" t="s">
         <v>16</v>
@@ -62488,7 +62489,7 @@
         <v>20</v>
       </c>
       <c r="D1410" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1410" t="s">
         <v>16</v>
@@ -62532,7 +62533,7 @@
         <v>20</v>
       </c>
       <c r="D1411" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1411" t="s">
         <v>16</v>
@@ -62576,7 +62577,7 @@
         <v>20</v>
       </c>
       <c r="D1412" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1412" t="s">
         <v>16</v>
@@ -62620,7 +62621,7 @@
         <v>20</v>
       </c>
       <c r="D1413" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1413" t="s">
         <v>16</v>
@@ -62664,7 +62665,7 @@
         <v>20</v>
       </c>
       <c r="D1414" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1414" t="s">
         <v>16</v>
@@ -62708,7 +62709,7 @@
         <v>20</v>
       </c>
       <c r="D1415" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1415" t="s">
         <v>16</v>
@@ -62752,7 +62753,7 @@
         <v>20</v>
       </c>
       <c r="D1416" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1416" t="s">
         <v>16</v>
@@ -62796,7 +62797,7 @@
         <v>20</v>
       </c>
       <c r="D1417" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1417" t="s">
         <v>16</v>
@@ -62840,7 +62841,7 @@
         <v>20</v>
       </c>
       <c r="D1418" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1418" t="s">
         <v>16</v>
@@ -62884,7 +62885,7 @@
         <v>20</v>
       </c>
       <c r="D1419" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1419" t="s">
         <v>16</v>
@@ -62928,7 +62929,7 @@
         <v>20</v>
       </c>
       <c r="D1420" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1420" t="s">
         <v>16</v>
@@ -62972,7 +62973,7 @@
         <v>20</v>
       </c>
       <c r="D1421" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1421" t="s">
         <v>16</v>
@@ -63016,7 +63017,7 @@
         <v>20</v>
       </c>
       <c r="D1422" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1422" t="s">
         <v>16</v>
@@ -63060,7 +63061,7 @@
         <v>20</v>
       </c>
       <c r="D1423" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1423" t="s">
         <v>16</v>
@@ -63104,7 +63105,7 @@
         <v>20</v>
       </c>
       <c r="D1424" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1424" t="s">
         <v>16</v>
@@ -63148,7 +63149,7 @@
         <v>20</v>
       </c>
       <c r="D1425" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1425" t="s">
         <v>16</v>
@@ -63192,7 +63193,7 @@
         <v>20</v>
       </c>
       <c r="D1426" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1426" t="s">
         <v>16</v>
@@ -63236,7 +63237,7 @@
         <v>20</v>
       </c>
       <c r="D1427" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1427" t="s">
         <v>16</v>
@@ -63280,7 +63281,7 @@
         <v>20</v>
       </c>
       <c r="D1428" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1428" t="s">
         <v>16</v>
@@ -63324,7 +63325,7 @@
         <v>20</v>
       </c>
       <c r="D1429" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1429" t="s">
         <v>16</v>
@@ -63368,7 +63369,7 @@
         <v>20</v>
       </c>
       <c r="D1430" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1430" t="s">
         <v>16</v>
@@ -63412,7 +63413,7 @@
         <v>20</v>
       </c>
       <c r="D1431" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1431" t="s">
         <v>16</v>
@@ -63456,7 +63457,7 @@
         <v>20</v>
       </c>
       <c r="D1432" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1432" t="s">
         <v>16</v>
@@ -63500,7 +63501,7 @@
         <v>20</v>
       </c>
       <c r="D1433" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1433" t="s">
         <v>16</v>
@@ -63544,7 +63545,7 @@
         <v>20</v>
       </c>
       <c r="D1434" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1434" t="s">
         <v>16</v>
@@ -63588,7 +63589,7 @@
         <v>20</v>
       </c>
       <c r="D1435" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1435" t="s">
         <v>16</v>
@@ -63632,7 +63633,7 @@
         <v>20</v>
       </c>
       <c r="D1436" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1436" t="s">
         <v>16</v>
@@ -63676,7 +63677,7 @@
         <v>20</v>
       </c>
       <c r="D1437" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1437" t="s">
         <v>16</v>
@@ -63720,7 +63721,7 @@
         <v>20</v>
       </c>
       <c r="D1438" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1438" t="s">
         <v>16</v>
@@ -63764,7 +63765,7 @@
         <v>20</v>
       </c>
       <c r="D1439" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1439" t="s">
         <v>16</v>
@@ -63808,7 +63809,7 @@
         <v>20</v>
       </c>
       <c r="D1440" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1440" t="s">
         <v>16</v>
@@ -63852,7 +63853,7 @@
         <v>20</v>
       </c>
       <c r="D1441" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1441" t="s">
         <v>16</v>
@@ -63896,7 +63897,7 @@
         <v>20</v>
       </c>
       <c r="D1442" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1442" t="s">
         <v>16</v>
@@ -63940,7 +63941,7 @@
         <v>20</v>
       </c>
       <c r="D1443" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1443" t="s">
         <v>16</v>
@@ -63984,7 +63985,7 @@
         <v>20</v>
       </c>
       <c r="D1444" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1444" t="s">
         <v>16</v>
@@ -64028,7 +64029,7 @@
         <v>20</v>
       </c>
       <c r="D1445" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1445" t="s">
         <v>16</v>
@@ -64072,7 +64073,7 @@
         <v>20</v>
       </c>
       <c r="D1446" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1446" t="s">
         <v>16</v>
@@ -64116,7 +64117,7 @@
         <v>20</v>
       </c>
       <c r="D1447" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1447" t="s">
         <v>16</v>
@@ -64160,7 +64161,7 @@
         <v>20</v>
       </c>
       <c r="D1448" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1448" t="s">
         <v>16</v>
@@ -64204,7 +64205,7 @@
         <v>20</v>
       </c>
       <c r="D1449" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1449" t="s">
         <v>16</v>
@@ -64248,7 +64249,7 @@
         <v>20</v>
       </c>
       <c r="D1450" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1450" t="s">
         <v>16</v>
@@ -64292,7 +64293,7 @@
         <v>20</v>
       </c>
       <c r="D1451" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1451" t="s">
         <v>16</v>
@@ -64336,7 +64337,7 @@
         <v>20</v>
       </c>
       <c r="D1452" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1452" t="s">
         <v>16</v>
